--- a/resultados/analisis_genero_tematico.xlsx
+++ b/resultados/analisis_genero_tematico.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="436">
   <si>
     <t>categoria</t>
   </si>
@@ -59,118 +59,118 @@
     <t>MOVILIDAD</t>
   </si>
   <si>
-    <t>0.011</t>
+    <t>0.01</t>
   </si>
   <si>
     <t>MUSICA_CULTURA</t>
   </si>
   <si>
-    <t>0.035</t>
+    <t>0.039</t>
   </si>
   <si>
     <t>Mujer</t>
   </si>
   <si>
+    <t>DROGAS</t>
+  </si>
+  <si>
+    <t>0.044</t>
+  </si>
+  <si>
     <t>ALCOHOL</t>
   </si>
   <si>
-    <t>0.08</t>
+    <t>0.061</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>DROGAS</t>
+    <t>RELIGION_IMAGINARIOS</t>
+  </si>
+  <si>
+    <t>0.195</t>
+  </si>
+  <si>
+    <t>DISCRIMINACION</t>
+  </si>
+  <si>
+    <t>0.221</t>
+  </si>
+  <si>
+    <t>DINERO_ESTATUS</t>
+  </si>
+  <si>
+    <t>CONSENTIMIENTO</t>
+  </si>
+  <si>
+    <t>0.233</t>
   </si>
   <si>
     <t>BAILE_FIESTA</t>
   </si>
   <si>
-    <t>0.151</t>
-  </si>
-  <si>
-    <t>RELIGION_IMAGINARIOS</t>
-  </si>
-  <si>
-    <t>0.154</t>
-  </si>
-  <si>
-    <t>CONSENTIMIENTO</t>
-  </si>
-  <si>
-    <t>0.228</t>
-  </si>
-  <si>
-    <t>DISCRIMINACION</t>
-  </si>
-  <si>
-    <t>0.249</t>
+    <t>0.252</t>
+  </si>
+  <si>
+    <t>TECNOLOGIA</t>
+  </si>
+  <si>
+    <t>0.307</t>
   </si>
   <si>
     <t>SEXUALIDAD</t>
   </si>
   <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>DINERO_ESTATUS</t>
-  </si>
-  <si>
-    <t>0.303</t>
-  </si>
-  <si>
-    <t>TECNOLOGIA</t>
-  </si>
-  <si>
-    <t>0.349</t>
+    <t>0.336</t>
   </si>
   <si>
     <t>DESAMOR</t>
   </si>
   <si>
-    <t>0.424</t>
+    <t>0.356</t>
   </si>
   <si>
     <t>VIDA_COTIDIANA</t>
   </si>
   <si>
-    <t>0.432</t>
+    <t>0.43</t>
   </si>
   <si>
     <t>GENERO_PODER</t>
   </si>
   <si>
-    <t>0.506</t>
+    <t>0.527</t>
   </si>
   <si>
     <t>NOCTURNIDAD</t>
   </si>
   <si>
-    <t>0.658</t>
+    <t>0.728</t>
+  </si>
+  <si>
+    <t>EMOCIONES</t>
+  </si>
+  <si>
+    <t>0.826</t>
+  </si>
+  <si>
+    <t>PRESTIGIO_CONFLICTO</t>
+  </si>
+  <si>
+    <t>0.982</t>
   </si>
   <si>
     <t>ROMANCE</t>
   </si>
   <si>
-    <t>0.848</t>
+    <t>0.985</t>
   </si>
   <si>
     <t>VIOLENCIA</t>
   </si>
   <si>
-    <t>0.863</t>
-  </si>
-  <si>
-    <t>EMOCIONES</t>
-  </si>
-  <si>
-    <t>0.945</t>
-  </si>
-  <si>
-    <t>PRESTIGIO_CONFLICTO</t>
-  </si>
-  <si>
-    <t>0.951</t>
+    <t>1</t>
   </si>
   <si>
     <t>año</t>
@@ -938,6 +938,12 @@
     <t>Bichota</t>
   </si>
   <si>
+    <t>Relación</t>
+  </si>
+  <si>
+    <t>Sech</t>
+  </si>
+  <si>
     <t>Sigues Con Él</t>
   </si>
   <si>
@@ -1040,12 +1046,6 @@
     <t>Arrebatá</t>
   </si>
   <si>
-    <t>BOBO</t>
-  </si>
-  <si>
-    <t>Mariah Angeliq, Bad Gyal y María Becerra</t>
-  </si>
-  <si>
     <t>Me Porto Bonito</t>
   </si>
   <si>
@@ -1121,7 +1121,7 @@
     <t>Rosalía</t>
   </si>
   <si>
-    <t>CANDY</t>
+    <t>Tití Me Preguntó</t>
   </si>
   <si>
     <t>TQG</t>
@@ -1702,19 +1702,19 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>2.1037</v>
+        <v>2.0997</v>
       </c>
       <c r="C2">
-        <v>0.8981</v>
+        <v>0.9123</v>
       </c>
       <c r="D2">
-        <v>1.2055</v>
+        <v>1.1875</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2">
-        <v>0.315</v>
+        <v>0.312</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
@@ -1728,19 +1728,19 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>2.3814</v>
+        <v>2.3623</v>
       </c>
       <c r="C3">
-        <v>1.5644</v>
+        <v>1.5719</v>
       </c>
       <c r="D3">
-        <v>0.8171</v>
+        <v>0.7904</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3">
-        <v>0.227</v>
+        <v>0.229</v>
       </c>
       <c r="G3" t="s">
         <v>10</v>
@@ -1754,19 +1754,19 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>0.3666</v>
+        <v>0.3642</v>
       </c>
       <c r="C4">
-        <v>0.1919</v>
+        <v>0.1936</v>
       </c>
       <c r="D4">
-        <v>0.1747</v>
+        <v>0.1706</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
       </c>
       <c r="F4">
-        <v>0.169</v>
+        <v>0.172</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
@@ -1780,19 +1780,19 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>0.3716</v>
+        <v>0.3693</v>
       </c>
       <c r="C5">
-        <v>0.4605</v>
+        <v>0.4717</v>
       </c>
       <c r="D5">
-        <v>-0.08890000000000001</v>
+        <v>-0.1024</v>
       </c>
       <c r="E5" t="s">
         <v>16</v>
       </c>
       <c r="F5">
-        <v>0.14</v>
+        <v>0.138</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
@@ -1806,22 +1806,22 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>0.427</v>
+        <v>0.4179</v>
       </c>
       <c r="C6">
-        <v>0.38</v>
+        <v>0.2089</v>
       </c>
       <c r="D6">
-        <v>0.0471</v>
+        <v>0.209</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
       <c r="F6">
-        <v>0.117</v>
+        <v>0.134</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -1829,25 +1829,25 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7">
+        <v>0.4416</v>
+      </c>
+      <c r="C7">
+        <v>0.3883</v>
+      </c>
+      <c r="D7">
+        <v>0.0533</v>
+      </c>
+      <c r="E7" t="s">
         <v>21</v>
       </c>
-      <c r="B7">
-        <v>0.4181</v>
-      </c>
-      <c r="C7">
-        <v>0.2162</v>
-      </c>
-      <c r="D7">
-        <v>0.2019</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
       <c r="F7">
-        <v>0.117</v>
+        <v>0.125</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
@@ -1855,51 +1855,51 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
+        <v>0.3783</v>
+      </c>
+      <c r="C8">
+        <v>0.6318</v>
+      </c>
+      <c r="D8">
+        <v>-0.2536</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="G8" t="s">
         <v>22</v>
       </c>
-      <c r="B8">
-        <v>1.3427</v>
-      </c>
-      <c r="C8">
-        <v>1.0969</v>
-      </c>
-      <c r="D8">
-        <v>0.2457</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8">
-        <v>0.096</v>
-      </c>
-      <c r="G8" t="s">
-        <v>20</v>
-      </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9">
-        <v>0.378</v>
+        <v>0.1512</v>
       </c>
       <c r="C9">
-        <v>0.6103</v>
+        <v>0.2546</v>
       </c>
       <c r="D9">
-        <v>-0.2323</v>
+        <v>-0.1034</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>0.095</v>
+        <v>0.082</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
@@ -1907,28 +1907,28 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10">
+        <v>0.256</v>
+      </c>
+      <c r="C10">
+        <v>0.2009</v>
+      </c>
+      <c r="D10">
+        <v>0.055</v>
+      </c>
+      <c r="E10" t="s">
         <v>26</v>
       </c>
-      <c r="B10">
-        <v>0.2188</v>
-      </c>
-      <c r="C10">
-        <v>0.5409</v>
-      </c>
-      <c r="D10">
-        <v>-0.3221</v>
-      </c>
-      <c r="E10" t="s">
-        <v>27</v>
-      </c>
       <c r="F10">
-        <v>0.08</v>
+        <v>0.082</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1936,22 +1936,22 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>0.1505</v>
+        <v>0.2157</v>
       </c>
       <c r="C11">
-        <v>0.2459</v>
+        <v>0.4965</v>
       </c>
       <c r="D11">
-        <v>-0.0954</v>
+        <v>-0.2808</v>
       </c>
       <c r="E11" t="s">
         <v>29</v>
       </c>
       <c r="F11">
-        <v>0.077</v>
+        <v>0.08</v>
       </c>
       <c r="G11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
@@ -1962,25 +1962,25 @@
         <v>30</v>
       </c>
       <c r="B12">
-        <v>1.0343</v>
+        <v>1.3235</v>
       </c>
       <c r="C12">
-        <v>1.0718</v>
+        <v>1.1356</v>
       </c>
       <c r="D12">
-        <v>-0.0375</v>
+        <v>0.1878</v>
       </c>
       <c r="E12" t="s">
         <v>31</v>
       </c>
       <c r="F12">
-        <v>0.073</v>
+        <v>0.076</v>
       </c>
       <c r="G12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1988,25 +1988,25 @@
         <v>32</v>
       </c>
       <c r="B13">
-        <v>0.2337</v>
+        <v>0.4015</v>
       </c>
       <c r="C13">
-        <v>0.3335</v>
+        <v>0.256</v>
       </c>
       <c r="D13">
-        <v>-0.0998</v>
+        <v>0.1456</v>
       </c>
       <c r="E13" t="s">
         <v>33</v>
       </c>
       <c r="F13">
-        <v>0.06900000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="G13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H13" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2014,25 +2014,25 @@
         <v>34</v>
       </c>
       <c r="B14">
-        <v>0.3868</v>
+        <v>1.0252</v>
       </c>
       <c r="C14">
-        <v>0.2881</v>
+        <v>1.1163</v>
       </c>
       <c r="D14">
-        <v>0.09859999999999999</v>
+        <v>-0.0911</v>
       </c>
       <c r="E14" t="s">
         <v>35</v>
       </c>
       <c r="F14">
-        <v>0.062</v>
+        <v>0.064</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H14" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2040,22 +2040,22 @@
         <v>36</v>
       </c>
       <c r="B15">
-        <v>0.9226</v>
+        <v>0.9095</v>
       </c>
       <c r="C15">
-        <v>0.9762999999999999</v>
+        <v>0.9768</v>
       </c>
       <c r="D15">
-        <v>-0.0537</v>
+        <v>-0.0673</v>
       </c>
       <c r="E15" t="s">
         <v>37</v>
       </c>
       <c r="F15">
-        <v>0.053</v>
+        <v>0.062</v>
       </c>
       <c r="G15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
@@ -2066,22 +2066,22 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>1.6274</v>
+        <v>1.6383</v>
       </c>
       <c r="C16">
-        <v>1.7434</v>
+        <v>1.7643</v>
       </c>
       <c r="D16">
-        <v>-0.1161</v>
+        <v>-0.1261</v>
       </c>
       <c r="E16" t="s">
         <v>39</v>
       </c>
       <c r="F16">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="G16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
@@ -2092,22 +2092,22 @@
         <v>40</v>
       </c>
       <c r="B17">
-        <v>2.9995</v>
+        <v>2.9652</v>
       </c>
       <c r="C17">
-        <v>3.0807</v>
+        <v>3.0757</v>
       </c>
       <c r="D17">
-        <v>-0.08119999999999999</v>
+        <v>-0.1105</v>
       </c>
       <c r="E17" t="s">
         <v>41</v>
       </c>
       <c r="F17">
-        <v>0.044</v>
+        <v>0.042</v>
       </c>
       <c r="G17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
@@ -2118,22 +2118,22 @@
         <v>42</v>
       </c>
       <c r="B18">
-        <v>0.5329</v>
+        <v>0.5253</v>
       </c>
       <c r="C18">
-        <v>0.5066000000000001</v>
+        <v>0.5026</v>
       </c>
       <c r="D18">
-        <v>0.0264</v>
+        <v>0.0228</v>
       </c>
       <c r="E18" t="s">
         <v>43</v>
       </c>
       <c r="F18">
-        <v>0.029</v>
+        <v>0.023</v>
       </c>
       <c r="G18" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
@@ -2144,22 +2144,22 @@
         <v>44</v>
       </c>
       <c r="B19">
-        <v>1.2971</v>
+        <v>0.6486</v>
       </c>
       <c r="C19">
-        <v>1.6507</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="D19">
-        <v>-0.3536</v>
+        <v>-0.1492</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
       </c>
       <c r="F19">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="G19" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
@@ -2170,22 +2170,22 @@
         <v>46</v>
       </c>
       <c r="B20">
-        <v>0.1802</v>
+        <v>0.214</v>
       </c>
       <c r="C20">
-        <v>0.1818</v>
+        <v>0.2389</v>
       </c>
       <c r="D20">
-        <v>-0.0016</v>
+        <v>-0.0249</v>
       </c>
       <c r="E20" t="s">
         <v>47</v>
       </c>
       <c r="F20">
-        <v>0.011</v>
+        <v>0.002</v>
       </c>
       <c r="G20" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
@@ -2196,22 +2196,22 @@
         <v>48</v>
       </c>
       <c r="B21">
-        <v>0.652</v>
+        <v>1.3241</v>
       </c>
       <c r="C21">
-        <v>0.7522</v>
+        <v>1.7046</v>
       </c>
       <c r="D21">
-        <v>-0.1002</v>
+        <v>-0.3805</v>
       </c>
       <c r="E21" t="s">
         <v>49</v>
       </c>
       <c r="F21">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="G21" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
@@ -2222,22 +2222,22 @@
         <v>50</v>
       </c>
       <c r="B22">
-        <v>0.2142</v>
+        <v>0.1776</v>
       </c>
       <c r="C22">
-        <v>0.2403</v>
+        <v>0.1882</v>
       </c>
       <c r="D22">
-        <v>-0.026</v>
+        <v>-0.0106</v>
       </c>
       <c r="E22" t="s">
         <v>51</v>
       </c>
       <c r="F22">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
@@ -2250,7 +2250,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y227"/>
+  <dimension ref="A1:Y226"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25" s="1" customFormat="1">
@@ -12203,13 +12203,13 @@
         <v>0</v>
       </c>
       <c r="G130">
-        <v>0.6578947368421052</v>
+        <v>0</v>
       </c>
       <c r="H130">
-        <v>5.921052631578947</v>
+        <v>2.18978102189781</v>
       </c>
       <c r="I130">
-        <v>0.6578947368421052</v>
+        <v>2.91970802919708</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -12221,10 +12221,10 @@
         <v>0</v>
       </c>
       <c r="M130">
-        <v>0</v>
+        <v>2.91970802919708</v>
       </c>
       <c r="N130">
-        <v>5.263157894736842</v>
+        <v>0.7299270072992701</v>
       </c>
       <c r="O130">
         <v>0</v>
@@ -12233,7 +12233,7 @@
         <v>0</v>
       </c>
       <c r="Q130">
-        <v>3.947368421052631</v>
+        <v>2.91970802919708</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -12245,16 +12245,16 @@
         <v>0</v>
       </c>
       <c r="U130">
-        <v>0</v>
+        <v>2.18978102189781</v>
       </c>
       <c r="V130">
-        <v>0.6578947368421052</v>
+        <v>2.91970802919708</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>0.7299270072992701</v>
       </c>
       <c r="X130">
-        <v>1.973684210526316</v>
+        <v>0.7299270072992701</v>
       </c>
       <c r="Y130">
         <v>0</v>
@@ -13189,43 +13189,43 @@
         <v>2019</v>
       </c>
       <c r="B143" t="s">
-        <v>221</v>
+        <v>294</v>
       </c>
       <c r="C143" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D143" t="s">
         <v>17</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>0.9345794392523363</v>
       </c>
       <c r="F143">
         <v>0</v>
       </c>
       <c r="G143">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="H143">
-        <v>1.666666666666667</v>
+        <v>1.869158878504673</v>
       </c>
       <c r="I143">
-        <v>0</v>
+        <v>2.803738317757009</v>
       </c>
       <c r="J143">
         <v>0</v>
       </c>
       <c r="K143">
-        <v>0</v>
+        <v>0.9345794392523363</v>
       </c>
       <c r="L143">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="M143">
-        <v>0</v>
+        <v>0.9345794392523363</v>
       </c>
       <c r="N143">
-        <v>1.666666666666667</v>
+        <v>0.9345794392523363</v>
       </c>
       <c r="O143">
         <v>0</v>
@@ -13234,31 +13234,31 @@
         <v>0</v>
       </c>
       <c r="Q143">
-        <v>0.8333333333333334</v>
+        <v>0.9345794392523363</v>
       </c>
       <c r="R143">
-        <v>0</v>
+        <v>0.9345794392523363</v>
       </c>
       <c r="S143">
-        <v>0.8333333333333334</v>
+        <v>0.9345794392523363</v>
       </c>
       <c r="T143">
-        <v>0</v>
+        <v>4.672897196261682</v>
       </c>
       <c r="U143">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="V143">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="W143">
         <v>0</v>
       </c>
       <c r="X143">
-        <v>0.8333333333333334</v>
+        <v>2.803738317757009</v>
       </c>
       <c r="Y143">
-        <v>0</v>
+        <v>0.9345794392523363</v>
       </c>
     </row>
     <row r="144" spans="1:25">
@@ -13266,7 +13266,7 @@
         <v>2019</v>
       </c>
       <c r="B144" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C144" t="s">
         <v>162</v>
@@ -13275,7 +13275,7 @@
         <v>17</v>
       </c>
       <c r="E144">
-        <v>0.9345794392523363</v>
+        <v>0</v>
       </c>
       <c r="F144">
         <v>0</v>
@@ -13284,25 +13284,25 @@
         <v>0</v>
       </c>
       <c r="H144">
-        <v>1.869158878504673</v>
+        <v>0</v>
       </c>
       <c r="I144">
-        <v>2.803738317757009</v>
+        <v>1.89873417721519</v>
       </c>
       <c r="J144">
         <v>0</v>
       </c>
       <c r="K144">
-        <v>0.9345794392523363</v>
+        <v>0</v>
       </c>
       <c r="L144">
         <v>0</v>
       </c>
       <c r="M144">
-        <v>0.9345794392523363</v>
+        <v>0.6329113924050633</v>
       </c>
       <c r="N144">
-        <v>0.9345794392523363</v>
+        <v>1.265822784810127</v>
       </c>
       <c r="O144">
         <v>0</v>
@@ -13311,31 +13311,31 @@
         <v>0</v>
       </c>
       <c r="Q144">
-        <v>0.9345794392523363</v>
+        <v>0</v>
       </c>
       <c r="R144">
-        <v>0.9345794392523363</v>
+        <v>0</v>
       </c>
       <c r="S144">
-        <v>0.9345794392523363</v>
+        <v>0</v>
       </c>
       <c r="T144">
-        <v>4.672897196261682</v>
+        <v>0</v>
       </c>
       <c r="U144">
-        <v>0</v>
+        <v>4.430379746835443</v>
       </c>
       <c r="V144">
-        <v>0</v>
+        <v>0.6329113924050633</v>
       </c>
       <c r="W144">
-        <v>0</v>
+        <v>1.265822784810127</v>
       </c>
       <c r="X144">
-        <v>2.803738317757009</v>
+        <v>4.430379746835443</v>
       </c>
       <c r="Y144">
-        <v>0.9345794392523363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:25">
@@ -13343,19 +13343,19 @@
         <v>2019</v>
       </c>
       <c r="B145" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C145" t="s">
-        <v>162</v>
+        <v>297</v>
       </c>
       <c r="D145" t="s">
         <v>17</v>
       </c>
       <c r="E145">
-        <v>0</v>
+        <v>5.46875</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>0.78125</v>
       </c>
       <c r="G145">
         <v>0</v>
@@ -13364,7 +13364,7 @@
         <v>0</v>
       </c>
       <c r="I145">
-        <v>1.89873417721519</v>
+        <v>0</v>
       </c>
       <c r="J145">
         <v>0</v>
@@ -13376,10 +13376,10 @@
         <v>0</v>
       </c>
       <c r="M145">
-        <v>0.6329113924050633</v>
+        <v>0</v>
       </c>
       <c r="N145">
-        <v>1.265822784810127</v>
+        <v>3.90625</v>
       </c>
       <c r="O145">
         <v>0</v>
@@ -13391,7 +13391,7 @@
         <v>0</v>
       </c>
       <c r="R145">
-        <v>0</v>
+        <v>1.5625</v>
       </c>
       <c r="S145">
         <v>0</v>
@@ -13400,16 +13400,16 @@
         <v>0</v>
       </c>
       <c r="U145">
-        <v>4.430379746835443</v>
+        <v>0.78125</v>
       </c>
       <c r="V145">
-        <v>0.6329113924050633</v>
+        <v>0.78125</v>
       </c>
       <c r="W145">
-        <v>1.265822784810127</v>
+        <v>0.78125</v>
       </c>
       <c r="X145">
-        <v>4.430379746835443</v>
+        <v>0</v>
       </c>
       <c r="Y145">
         <v>0</v>
@@ -13417,31 +13417,31 @@
     </row>
     <row r="146" spans="1:25">
       <c r="A146">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B146" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C146" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D146" t="s">
         <v>17</v>
       </c>
       <c r="E146">
-        <v>5.46875</v>
+        <v>1.923076923076923</v>
       </c>
       <c r="F146">
-        <v>0.78125</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="H146">
         <v>0</v>
       </c>
       <c r="I146">
-        <v>0</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="J146">
         <v>0</v>
@@ -13453,10 +13453,10 @@
         <v>0</v>
       </c>
       <c r="M146">
-        <v>0</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="N146">
-        <v>3.90625</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="O146">
         <v>0</v>
@@ -13468,7 +13468,7 @@
         <v>0</v>
       </c>
       <c r="R146">
-        <v>1.5625</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="S146">
         <v>0</v>
@@ -13477,19 +13477,19 @@
         <v>0</v>
       </c>
       <c r="U146">
-        <v>0.78125</v>
+        <v>1.923076923076923</v>
       </c>
       <c r="V146">
-        <v>0.78125</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="W146">
-        <v>0.78125</v>
+        <v>0</v>
       </c>
       <c r="X146">
-        <v>0</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="Y146">
-        <v>0</v>
+        <v>0.3846153846153846</v>
       </c>
     </row>
     <row r="147" spans="1:25">
@@ -13497,46 +13497,46 @@
         <v>2020</v>
       </c>
       <c r="B147" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C147" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D147" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E147">
-        <v>1.923076923076923</v>
+        <v>0.2597402597402597</v>
       </c>
       <c r="F147">
-        <v>1.538461538461539</v>
+        <v>0.7792207792207793</v>
       </c>
       <c r="G147">
-        <v>1.538461538461539</v>
+        <v>4.675324675324675</v>
       </c>
       <c r="H147">
         <v>0</v>
       </c>
       <c r="I147">
-        <v>1.538461538461539</v>
+        <v>0</v>
       </c>
       <c r="J147">
         <v>0</v>
       </c>
       <c r="K147">
-        <v>0</v>
+        <v>0.2597402597402597</v>
       </c>
       <c r="L147">
-        <v>0</v>
+        <v>1.818181818181818</v>
       </c>
       <c r="M147">
-        <v>1.153846153846154</v>
+        <v>0</v>
       </c>
       <c r="N147">
-        <v>0.3846153846153846</v>
+        <v>5.454545454545454</v>
       </c>
       <c r="O147">
-        <v>0</v>
+        <v>0.5194805194805194</v>
       </c>
       <c r="P147">
         <v>0</v>
@@ -13545,28 +13545,28 @@
         <v>0</v>
       </c>
       <c r="R147">
-        <v>1.538461538461539</v>
+        <v>4.675324675324675</v>
       </c>
       <c r="S147">
-        <v>0</v>
+        <v>0.2597402597402597</v>
       </c>
       <c r="T147">
-        <v>0</v>
+        <v>0.2597402597402597</v>
       </c>
       <c r="U147">
-        <v>1.923076923076923</v>
+        <v>0.2597402597402597</v>
       </c>
       <c r="V147">
-        <v>0.3846153846153846</v>
+        <v>7.012987012987012</v>
       </c>
       <c r="W147">
-        <v>0</v>
+        <v>0.5194805194805194</v>
       </c>
       <c r="X147">
-        <v>0.3846153846153846</v>
+        <v>4.415584415584416</v>
       </c>
       <c r="Y147">
-        <v>0.3846153846153846</v>
+        <v>0.2597402597402597</v>
       </c>
     </row>
     <row r="148" spans="1:25">
@@ -13574,46 +13574,46 @@
         <v>2020</v>
       </c>
       <c r="B148" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C148" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D148" t="s">
         <v>11</v>
       </c>
       <c r="E148">
-        <v>0.2597402597402597</v>
+        <v>0</v>
       </c>
       <c r="F148">
-        <v>0.7792207792207793</v>
+        <v>0</v>
       </c>
       <c r="G148">
-        <v>4.675324675324675</v>
+        <v>0</v>
       </c>
       <c r="H148">
-        <v>0</v>
+        <v>1.342281879194631</v>
       </c>
       <c r="I148">
-        <v>0</v>
+        <v>1.342281879194631</v>
       </c>
       <c r="J148">
         <v>0</v>
       </c>
       <c r="K148">
-        <v>0.2597402597402597</v>
+        <v>0</v>
       </c>
       <c r="L148">
-        <v>1.818181818181818</v>
+        <v>0.6711409395973155</v>
       </c>
       <c r="M148">
-        <v>0</v>
+        <v>0.6711409395973155</v>
       </c>
       <c r="N148">
-        <v>5.454545454545454</v>
+        <v>5.369127516778524</v>
       </c>
       <c r="O148">
-        <v>0.5194805194805194</v>
+        <v>0</v>
       </c>
       <c r="P148">
         <v>0</v>
@@ -13622,28 +13622,28 @@
         <v>0</v>
       </c>
       <c r="R148">
-        <v>4.675324675324675</v>
+        <v>0</v>
       </c>
       <c r="S148">
-        <v>0.2597402597402597</v>
+        <v>0.6711409395973155</v>
       </c>
       <c r="T148">
-        <v>0.2597402597402597</v>
+        <v>1.342281879194631</v>
       </c>
       <c r="U148">
-        <v>0.2597402597402597</v>
+        <v>1.342281879194631</v>
       </c>
       <c r="V148">
-        <v>7.012987012987012</v>
+        <v>0</v>
       </c>
       <c r="W148">
-        <v>0.5194805194805194</v>
+        <v>4.026845637583892</v>
       </c>
       <c r="X148">
-        <v>4.415584415584416</v>
+        <v>1.342281879194631</v>
       </c>
       <c r="Y148">
-        <v>0.2597402597402597</v>
+        <v>0.6711409395973155</v>
       </c>
     </row>
     <row r="149" spans="1:25">
@@ -13651,28 +13651,28 @@
         <v>2020</v>
       </c>
       <c r="B149" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C149" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D149" t="s">
         <v>11</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>1.395348837209302</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>7.441860465116279</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>3.255813953488372</v>
       </c>
       <c r="H149">
-        <v>1.342281879194631</v>
+        <v>0</v>
       </c>
       <c r="I149">
-        <v>1.342281879194631</v>
+        <v>10.23255813953488</v>
       </c>
       <c r="J149">
         <v>0</v>
@@ -13681,13 +13681,13 @@
         <v>0</v>
       </c>
       <c r="L149">
-        <v>0.6711409395973155</v>
+        <v>0</v>
       </c>
       <c r="M149">
-        <v>0.6711409395973155</v>
+        <v>0.9302325581395349</v>
       </c>
       <c r="N149">
-        <v>5.369127516778524</v>
+        <v>4.186046511627907</v>
       </c>
       <c r="O149">
         <v>0</v>
@@ -13696,31 +13696,31 @@
         <v>0</v>
       </c>
       <c r="Q149">
-        <v>0</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="R149">
-        <v>0</v>
+        <v>1.395348837209302</v>
       </c>
       <c r="S149">
-        <v>0.6711409395973155</v>
+        <v>0</v>
       </c>
       <c r="T149">
-        <v>1.342281879194631</v>
+        <v>0</v>
       </c>
       <c r="U149">
-        <v>1.342281879194631</v>
+        <v>0.9302325581395349</v>
       </c>
       <c r="V149">
         <v>0</v>
       </c>
       <c r="W149">
-        <v>4.026845637583892</v>
+        <v>0</v>
       </c>
       <c r="X149">
-        <v>1.342281879194631</v>
+        <v>1.395348837209302</v>
       </c>
       <c r="Y149">
-        <v>0.6711409395973155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:25">
@@ -13728,28 +13728,28 @@
         <v>2020</v>
       </c>
       <c r="B150" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C150" t="s">
-        <v>305</v>
+        <v>159</v>
       </c>
       <c r="D150" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E150">
-        <v>1.395348837209302</v>
+        <v>0.5649717514124294</v>
       </c>
       <c r="F150">
-        <v>7.441860465116279</v>
+        <v>1.694915254237288</v>
       </c>
       <c r="G150">
-        <v>3.255813953488372</v>
+        <v>2.259887005649718</v>
       </c>
       <c r="H150">
         <v>0</v>
       </c>
       <c r="I150">
-        <v>10.23255813953488</v>
+        <v>0</v>
       </c>
       <c r="J150">
         <v>0</v>
@@ -13758,25 +13758,25 @@
         <v>0</v>
       </c>
       <c r="L150">
-        <v>0</v>
+        <v>0.5649717514124294</v>
       </c>
       <c r="M150">
-        <v>0.9302325581395349</v>
+        <v>0.5649717514124294</v>
       </c>
       <c r="N150">
-        <v>4.186046511627907</v>
+        <v>2.259887005649718</v>
       </c>
       <c r="O150">
-        <v>0</v>
+        <v>0.5649717514124294</v>
       </c>
       <c r="P150">
         <v>0</v>
       </c>
       <c r="Q150">
-        <v>0.4651162790697674</v>
+        <v>0</v>
       </c>
       <c r="R150">
-        <v>1.395348837209302</v>
+        <v>25.98870056497175</v>
       </c>
       <c r="S150">
         <v>0</v>
@@ -13785,19 +13785,19 @@
         <v>0</v>
       </c>
       <c r="U150">
-        <v>0.9302325581395349</v>
+        <v>0</v>
       </c>
       <c r="V150">
-        <v>0</v>
+        <v>2.259887005649718</v>
       </c>
       <c r="W150">
-        <v>0</v>
+        <v>1.694915254237288</v>
       </c>
       <c r="X150">
-        <v>1.395348837209302</v>
+        <v>0.5649717514124294</v>
       </c>
       <c r="Y150">
-        <v>0</v>
+        <v>0.5649717514124294</v>
       </c>
     </row>
     <row r="151" spans="1:25">
@@ -13805,22 +13805,22 @@
         <v>2020</v>
       </c>
       <c r="B151" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C151" t="s">
-        <v>159</v>
+        <v>308</v>
       </c>
       <c r="D151" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E151">
-        <v>0.5649717514124294</v>
+        <v>2.5</v>
       </c>
       <c r="F151">
-        <v>1.694915254237288</v>
+        <v>0</v>
       </c>
       <c r="G151">
-        <v>2.259887005649718</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -13835,25 +13835,25 @@
         <v>0</v>
       </c>
       <c r="L151">
-        <v>0.5649717514124294</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="M151">
-        <v>0.5649717514124294</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N151">
-        <v>2.259887005649718</v>
+        <v>0</v>
       </c>
       <c r="O151">
-        <v>0.5649717514124294</v>
+        <v>0</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="Q151">
         <v>0</v>
       </c>
       <c r="R151">
-        <v>25.98870056497175</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="S151">
         <v>0</v>
@@ -13865,16 +13865,16 @@
         <v>0</v>
       </c>
       <c r="V151">
-        <v>2.259887005649718</v>
+        <v>0</v>
       </c>
       <c r="W151">
-        <v>1.694915254237288</v>
+        <v>1.25</v>
       </c>
       <c r="X151">
-        <v>0.5649717514124294</v>
+        <v>0</v>
       </c>
       <c r="Y151">
-        <v>0.5649717514124294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:25">
@@ -13882,10 +13882,10 @@
         <v>2020</v>
       </c>
       <c r="B152" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C152" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D152" t="s">
         <v>11</v>
@@ -13959,10 +13959,10 @@
         <v>2020</v>
       </c>
       <c r="B153" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C153" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D153" t="s">
         <v>11</v>
@@ -14036,7 +14036,7 @@
         <v>2020</v>
       </c>
       <c r="B154" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C154" t="s">
         <v>238</v>
@@ -14113,10 +14113,10 @@
         <v>2020</v>
       </c>
       <c r="B155" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C155" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D155" t="s">
         <v>11</v>
@@ -14190,7 +14190,7 @@
         <v>2020</v>
       </c>
       <c r="B156" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C156" t="s">
         <v>159</v>
@@ -14267,7 +14267,7 @@
         <v>2020</v>
       </c>
       <c r="B157" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C157" t="s">
         <v>162</v>
@@ -14344,10 +14344,10 @@
         <v>2020</v>
       </c>
       <c r="B158" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C158" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D158" t="s">
         <v>17</v>
@@ -14421,10 +14421,10 @@
         <v>2020</v>
       </c>
       <c r="B159" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C159" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D159" t="s">
         <v>17</v>
@@ -14498,10 +14498,10 @@
         <v>2020</v>
       </c>
       <c r="B160" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C160" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D160" t="s">
         <v>17</v>
@@ -14575,10 +14575,10 @@
         <v>2021</v>
       </c>
       <c r="B161" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C161" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D161" t="s">
         <v>11</v>
@@ -14652,10 +14652,10 @@
         <v>2021</v>
       </c>
       <c r="B162" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C162" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D162" t="s">
         <v>11</v>
@@ -14729,7 +14729,7 @@
         <v>2021</v>
       </c>
       <c r="B163" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C163" t="s">
         <v>305</v>
@@ -14806,10 +14806,10 @@
         <v>2021</v>
       </c>
       <c r="B164" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C164" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D164" t="s">
         <v>17</v>
@@ -14883,7 +14883,7 @@
         <v>2021</v>
       </c>
       <c r="B165" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C165" t="s">
         <v>224</v>
@@ -14960,10 +14960,10 @@
         <v>2021</v>
       </c>
       <c r="B166" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C166" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D166" t="s">
         <v>11</v>
@@ -15037,10 +15037,10 @@
         <v>2021</v>
       </c>
       <c r="B167" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C167" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D167" t="s">
         <v>11</v>
@@ -15114,7 +15114,7 @@
         <v>2021</v>
       </c>
       <c r="B168" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C168" t="s">
         <v>78</v>
@@ -15191,7 +15191,7 @@
         <v>2021</v>
       </c>
       <c r="B169" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C169" t="s">
         <v>159</v>
@@ -15268,10 +15268,10 @@
         <v>2021</v>
       </c>
       <c r="B170" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C170" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D170" t="s">
         <v>17</v>
@@ -15345,10 +15345,10 @@
         <v>2021</v>
       </c>
       <c r="B171" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C171" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D171" t="s">
         <v>17</v>
@@ -15422,7 +15422,7 @@
         <v>2021</v>
       </c>
       <c r="B172" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C172" t="s">
         <v>162</v>
@@ -15496,31 +15496,31 @@
     </row>
     <row r="173" spans="1:25">
       <c r="A173">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B173" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C173" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D173" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E173">
-        <v>0.4329004329004329</v>
+        <v>0</v>
       </c>
       <c r="F173">
-        <v>0</v>
+        <v>0.641025641025641</v>
       </c>
       <c r="G173">
-        <v>0</v>
+        <v>2.564102564102564</v>
       </c>
       <c r="H173">
-        <v>0</v>
+        <v>0.641025641025641</v>
       </c>
       <c r="I173">
-        <v>0.4329004329004329</v>
+        <v>0.641025641025641</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -15529,25 +15529,25 @@
         <v>0</v>
       </c>
       <c r="L173">
-        <v>0.4329004329004329</v>
+        <v>1.282051282051282</v>
       </c>
       <c r="M173">
-        <v>1.298701298701299</v>
+        <v>0</v>
       </c>
       <c r="N173">
-        <v>3.463203463203463</v>
+        <v>6.41025641025641</v>
       </c>
       <c r="O173">
-        <v>0.4329004329004329</v>
+        <v>0.641025641025641</v>
       </c>
       <c r="P173">
-        <v>0.4329004329004329</v>
+        <v>0</v>
       </c>
       <c r="Q173">
-        <v>0</v>
+        <v>0.641025641025641</v>
       </c>
       <c r="R173">
-        <v>2.164502164502164</v>
+        <v>4.487179487179487</v>
       </c>
       <c r="S173">
         <v>0</v>
@@ -15556,16 +15556,16 @@
         <v>0</v>
       </c>
       <c r="U173">
-        <v>1.731601731601732</v>
+        <v>2.564102564102564</v>
       </c>
       <c r="V173">
-        <v>0.8658008658008658</v>
+        <v>3.846153846153846</v>
       </c>
       <c r="W173">
-        <v>4.329004329004329</v>
+        <v>1.282051282051282</v>
       </c>
       <c r="X173">
-        <v>0.4329004329004329</v>
+        <v>0</v>
       </c>
       <c r="Y173">
         <v>0</v>
@@ -15576,73 +15576,73 @@
         <v>2022</v>
       </c>
       <c r="B174" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C174" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D174" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E174">
-        <v>0</v>
+        <v>1.025641025641026</v>
       </c>
       <c r="F174">
-        <v>0.641025641025641</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="G174">
-        <v>2.564102564102564</v>
+        <v>0</v>
       </c>
       <c r="H174">
-        <v>0.641025641025641</v>
+        <v>1.025641025641026</v>
       </c>
       <c r="I174">
-        <v>0.641025641025641</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="J174">
         <v>0</v>
       </c>
       <c r="K174">
-        <v>0</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="L174">
-        <v>1.282051282051282</v>
+        <v>0</v>
       </c>
       <c r="M174">
         <v>0</v>
       </c>
       <c r="N174">
-        <v>6.41025641025641</v>
+        <v>3.076923076923077</v>
       </c>
       <c r="O174">
-        <v>0.641025641025641</v>
+        <v>1.025641025641026</v>
       </c>
       <c r="P174">
         <v>0</v>
       </c>
       <c r="Q174">
-        <v>0.641025641025641</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="R174">
-        <v>4.487179487179487</v>
+        <v>0</v>
       </c>
       <c r="S174">
-        <v>0</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="T174">
-        <v>0</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="U174">
-        <v>2.564102564102564</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="V174">
-        <v>3.846153846153846</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="W174">
-        <v>1.282051282051282</v>
+        <v>0</v>
       </c>
       <c r="X174">
-        <v>0</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="Y174">
         <v>0</v>
@@ -15653,73 +15653,73 @@
         <v>2022</v>
       </c>
       <c r="B175" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C175" t="s">
-        <v>346</v>
+        <v>305</v>
       </c>
       <c r="D175" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E175">
-        <v>1.025641025641026</v>
+        <v>1.932367149758454</v>
       </c>
       <c r="F175">
-        <v>0.5128205128205128</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="G175">
-        <v>0</v>
+        <v>1.449275362318841</v>
       </c>
       <c r="H175">
-        <v>1.025641025641026</v>
+        <v>1.449275362318841</v>
       </c>
       <c r="I175">
-        <v>0.5128205128205128</v>
+        <v>0</v>
       </c>
       <c r="J175">
         <v>0</v>
       </c>
       <c r="K175">
-        <v>0.5128205128205128</v>
+        <v>0</v>
       </c>
       <c r="L175">
-        <v>0</v>
+        <v>1.932367149758454</v>
       </c>
       <c r="M175">
-        <v>0</v>
+        <v>0.4830917874396135</v>
       </c>
       <c r="N175">
-        <v>3.076923076923077</v>
+        <v>3.864734299516908</v>
       </c>
       <c r="O175">
-        <v>1.025641025641026</v>
+        <v>0.4830917874396135</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>0.4830917874396135</v>
       </c>
       <c r="Q175">
-        <v>0.5128205128205128</v>
+        <v>0.966183574879227</v>
       </c>
       <c r="R175">
         <v>0</v>
       </c>
       <c r="S175">
-        <v>1.538461538461539</v>
+        <v>0</v>
       </c>
       <c r="T175">
-        <v>0.5128205128205128</v>
+        <v>0</v>
       </c>
       <c r="U175">
-        <v>0.5128205128205128</v>
+        <v>0</v>
       </c>
       <c r="V175">
-        <v>0.5128205128205128</v>
+        <v>6.763285024154589</v>
       </c>
       <c r="W175">
-        <v>0</v>
+        <v>1.932367149758454</v>
       </c>
       <c r="X175">
-        <v>1.538461538461539</v>
+        <v>2.898550724637681</v>
       </c>
       <c r="Y175">
         <v>0</v>
@@ -15730,25 +15730,25 @@
         <v>2022</v>
       </c>
       <c r="B176" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C176" t="s">
-        <v>305</v>
+        <v>159</v>
       </c>
       <c r="D176" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E176">
-        <v>1.932367149758454</v>
+        <v>0</v>
       </c>
       <c r="F176">
-        <v>4.347826086956522</v>
+        <v>1.234567901234568</v>
       </c>
       <c r="G176">
-        <v>1.449275362318841</v>
+        <v>2.469135802469136</v>
       </c>
       <c r="H176">
-        <v>1.449275362318841</v>
+        <v>0</v>
       </c>
       <c r="I176">
         <v>0</v>
@@ -15760,25 +15760,25 @@
         <v>0</v>
       </c>
       <c r="L176">
-        <v>1.932367149758454</v>
+        <v>1.234567901234568</v>
       </c>
       <c r="M176">
-        <v>0.4830917874396135</v>
+        <v>0</v>
       </c>
       <c r="N176">
-        <v>3.864734299516908</v>
+        <v>3.703703703703703</v>
       </c>
       <c r="O176">
-        <v>0.4830917874396135</v>
+        <v>0</v>
       </c>
       <c r="P176">
-        <v>0.4830917874396135</v>
+        <v>0</v>
       </c>
       <c r="Q176">
-        <v>0.966183574879227</v>
+        <v>0</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>0.6172839506172839</v>
       </c>
       <c r="S176">
         <v>0</v>
@@ -15787,16 +15787,16 @@
         <v>0</v>
       </c>
       <c r="U176">
-        <v>0</v>
+        <v>0.6172839506172839</v>
       </c>
       <c r="V176">
-        <v>6.763285024154589</v>
+        <v>0</v>
       </c>
       <c r="W176">
-        <v>1.932367149758454</v>
+        <v>0</v>
       </c>
       <c r="X176">
-        <v>2.898550724637681</v>
+        <v>8.024691358024691</v>
       </c>
       <c r="Y176">
         <v>0</v>
@@ -15807,22 +15807,22 @@
         <v>2022</v>
       </c>
       <c r="B177" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C177" t="s">
-        <v>159</v>
+        <v>325</v>
       </c>
       <c r="D177" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="F177">
-        <v>1.234567901234568</v>
+        <v>2.564102564102564</v>
       </c>
       <c r="G177">
-        <v>2.469135802469136</v>
+        <v>0</v>
       </c>
       <c r="H177">
         <v>0</v>
@@ -15831,49 +15831,49 @@
         <v>0</v>
       </c>
       <c r="J177">
-        <v>0</v>
+        <v>1.025641025641026</v>
       </c>
       <c r="K177">
-        <v>0</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="L177">
-        <v>1.234567901234568</v>
+        <v>0</v>
       </c>
       <c r="M177">
         <v>0</v>
       </c>
       <c r="N177">
-        <v>3.703703703703703</v>
+        <v>4.615384615384616</v>
       </c>
       <c r="O177">
         <v>0</v>
       </c>
       <c r="P177">
-        <v>0</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="Q177">
-        <v>0</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="R177">
-        <v>0.6172839506172839</v>
+        <v>0</v>
       </c>
       <c r="S177">
         <v>0</v>
       </c>
       <c r="T177">
-        <v>0</v>
+        <v>3.589743589743589</v>
       </c>
       <c r="U177">
-        <v>0.6172839506172839</v>
+        <v>0</v>
       </c>
       <c r="V177">
-        <v>0</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="W177">
-        <v>0</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="X177">
-        <v>8.024691358024691</v>
+        <v>3.076923076923077</v>
       </c>
       <c r="Y177">
         <v>0</v>
@@ -15884,34 +15884,34 @@
         <v>2022</v>
       </c>
       <c r="B178" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C178" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="D178" t="s">
         <v>11</v>
       </c>
       <c r="E178">
-        <v>0.5128205128205128</v>
+        <v>0</v>
       </c>
       <c r="F178">
-        <v>2.564102564102564</v>
+        <v>0.4739336492890995</v>
       </c>
       <c r="G178">
-        <v>0</v>
+        <v>1.421800947867299</v>
       </c>
       <c r="H178">
         <v>0</v>
       </c>
       <c r="I178">
-        <v>0</v>
+        <v>1.421800947867299</v>
       </c>
       <c r="J178">
-        <v>1.025641025641026</v>
+        <v>0</v>
       </c>
       <c r="K178">
-        <v>0.5128205128205128</v>
+        <v>0</v>
       </c>
       <c r="L178">
         <v>0</v>
@@ -15920,37 +15920,37 @@
         <v>0</v>
       </c>
       <c r="N178">
-        <v>4.615384615384616</v>
+        <v>0.9478672985781991</v>
       </c>
       <c r="O178">
         <v>0</v>
       </c>
       <c r="P178">
-        <v>0.5128205128205128</v>
+        <v>0</v>
       </c>
       <c r="Q178">
-        <v>0.5128205128205128</v>
+        <v>0</v>
       </c>
       <c r="R178">
         <v>0</v>
       </c>
       <c r="S178">
-        <v>0</v>
+        <v>0.4739336492890995</v>
       </c>
       <c r="T178">
-        <v>3.589743589743589</v>
+        <v>0.4739336492890995</v>
       </c>
       <c r="U178">
-        <v>0</v>
+        <v>1.421800947867299</v>
       </c>
       <c r="V178">
-        <v>1.538461538461539</v>
+        <v>5.213270142180095</v>
       </c>
       <c r="W178">
-        <v>0.5128205128205128</v>
+        <v>0</v>
       </c>
       <c r="X178">
-        <v>3.076923076923077</v>
+        <v>0.4739336492890995</v>
       </c>
       <c r="Y178">
         <v>0</v>
@@ -15961,28 +15961,28 @@
         <v>2022</v>
       </c>
       <c r="B179" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C179" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D179" t="s">
         <v>11</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>0.6644518272425249</v>
       </c>
       <c r="F179">
-        <v>0.4739336492890995</v>
+        <v>32.89036544850498</v>
       </c>
       <c r="G179">
-        <v>1.421800947867299</v>
+        <v>0</v>
       </c>
       <c r="H179">
-        <v>0</v>
+        <v>0.6644518272425249</v>
       </c>
       <c r="I179">
-        <v>1.421800947867299</v>
+        <v>0.6644518272425249</v>
       </c>
       <c r="J179">
         <v>0</v>
@@ -15991,13 +15991,13 @@
         <v>0</v>
       </c>
       <c r="L179">
-        <v>0</v>
+        <v>0.6644518272425249</v>
       </c>
       <c r="M179">
         <v>0</v>
       </c>
       <c r="N179">
-        <v>0.9478672985781991</v>
+        <v>1.661129568106313</v>
       </c>
       <c r="O179">
         <v>0</v>
@@ -16006,28 +16006,28 @@
         <v>0</v>
       </c>
       <c r="Q179">
-        <v>0</v>
+        <v>0.6644518272425249</v>
       </c>
       <c r="R179">
-        <v>0</v>
+        <v>4.651162790697675</v>
       </c>
       <c r="S179">
-        <v>0.4739336492890995</v>
+        <v>0.3322259136212625</v>
       </c>
       <c r="T179">
-        <v>0.4739336492890995</v>
+        <v>0</v>
       </c>
       <c r="U179">
-        <v>1.421800947867299</v>
+        <v>0</v>
       </c>
       <c r="V179">
-        <v>5.213270142180095</v>
+        <v>2.990033222591362</v>
       </c>
       <c r="W179">
         <v>0</v>
       </c>
       <c r="X179">
-        <v>0.4739336492890995</v>
+        <v>1.661129568106313</v>
       </c>
       <c r="Y179">
         <v>0</v>
@@ -16038,73 +16038,73 @@
         <v>2022</v>
       </c>
       <c r="B180" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C180" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D180" t="s">
         <v>11</v>
       </c>
       <c r="E180">
-        <v>0.6644518272425249</v>
+        <v>1.84331797235023</v>
       </c>
       <c r="F180">
-        <v>32.89036544850498</v>
+        <v>0</v>
       </c>
       <c r="G180">
-        <v>0</v>
+        <v>0.9216589861751152</v>
       </c>
       <c r="H180">
-        <v>0.6644518272425249</v>
+        <v>0</v>
       </c>
       <c r="I180">
-        <v>0.6644518272425249</v>
+        <v>0</v>
       </c>
       <c r="J180">
-        <v>0</v>
+        <v>0.4608294930875576</v>
       </c>
       <c r="K180">
-        <v>0</v>
+        <v>0.4608294930875576</v>
       </c>
       <c r="L180">
-        <v>0.6644518272425249</v>
+        <v>0</v>
       </c>
       <c r="M180">
-        <v>0</v>
+        <v>3.225806451612903</v>
       </c>
       <c r="N180">
-        <v>1.661129568106313</v>
+        <v>2.764976958525346</v>
       </c>
       <c r="O180">
-        <v>0</v>
+        <v>0.4608294930875576</v>
       </c>
       <c r="P180">
         <v>0</v>
       </c>
       <c r="Q180">
-        <v>0.6644518272425249</v>
+        <v>3.686635944700461</v>
       </c>
       <c r="R180">
-        <v>4.651162790697675</v>
+        <v>1.382488479262673</v>
       </c>
       <c r="S180">
-        <v>0.3322259136212625</v>
+        <v>1.382488479262673</v>
       </c>
       <c r="T180">
-        <v>0</v>
+        <v>0.9216589861751152</v>
       </c>
       <c r="U180">
-        <v>0</v>
+        <v>1.382488479262673</v>
       </c>
       <c r="V180">
-        <v>2.990033222591362</v>
+        <v>2.764976958525346</v>
       </c>
       <c r="W180">
         <v>0</v>
       </c>
       <c r="X180">
-        <v>1.661129568106313</v>
+        <v>3.225806451612903</v>
       </c>
       <c r="Y180">
         <v>0</v>
@@ -16115,76 +16115,76 @@
         <v>2022</v>
       </c>
       <c r="B181" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C181" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D181" t="s">
         <v>11</v>
       </c>
       <c r="E181">
-        <v>1.84331797235023</v>
+        <v>3.041825095057034</v>
       </c>
       <c r="F181">
-        <v>0</v>
+        <v>1.140684410646388</v>
       </c>
       <c r="G181">
-        <v>0.9216589861751152</v>
+        <v>1.520912547528517</v>
       </c>
       <c r="H181">
-        <v>0</v>
+        <v>0.3802281368821293</v>
       </c>
       <c r="I181">
         <v>0</v>
       </c>
       <c r="J181">
-        <v>0.4608294930875576</v>
+        <v>0.7604562737642585</v>
       </c>
       <c r="K181">
-        <v>0.4608294930875576</v>
+        <v>0</v>
       </c>
       <c r="L181">
         <v>0</v>
       </c>
       <c r="M181">
-        <v>3.225806451612903</v>
+        <v>0.3802281368821293</v>
       </c>
       <c r="N181">
-        <v>2.764976958525346</v>
+        <v>0</v>
       </c>
       <c r="O181">
-        <v>0.4608294930875576</v>
+        <v>0.7604562737642585</v>
       </c>
       <c r="P181">
-        <v>0</v>
+        <v>0.7604562737642585</v>
       </c>
       <c r="Q181">
-        <v>3.686635944700461</v>
+        <v>0.7604562737642585</v>
       </c>
       <c r="R181">
-        <v>1.382488479262673</v>
+        <v>0.7604562737642585</v>
       </c>
       <c r="S181">
-        <v>1.382488479262673</v>
+        <v>0</v>
       </c>
       <c r="T181">
-        <v>0.9216589861751152</v>
+        <v>0</v>
       </c>
       <c r="U181">
-        <v>1.382488479262673</v>
+        <v>0</v>
       </c>
       <c r="V181">
-        <v>2.764976958525346</v>
+        <v>0.7604562737642585</v>
       </c>
       <c r="W181">
-        <v>0</v>
+        <v>0.7604562737642585</v>
       </c>
       <c r="X181">
-        <v>3.225806451612903</v>
+        <v>1.140684410646388</v>
       </c>
       <c r="Y181">
-        <v>0</v>
+        <v>0.3802281368821293</v>
       </c>
     </row>
     <row r="182" spans="1:25">
@@ -16192,31 +16192,31 @@
         <v>2022</v>
       </c>
       <c r="B182" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C182" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D182" t="s">
         <v>11</v>
       </c>
       <c r="E182">
-        <v>3.041825095057034</v>
+        <v>0</v>
       </c>
       <c r="F182">
-        <v>1.140684410646388</v>
+        <v>0</v>
       </c>
       <c r="G182">
-        <v>1.520912547528517</v>
+        <v>0</v>
       </c>
       <c r="H182">
-        <v>0.3802281368821293</v>
+        <v>0</v>
       </c>
       <c r="I182">
-        <v>0</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="J182">
-        <v>0.7604562737642585</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="K182">
         <v>0</v>
@@ -16225,43 +16225,43 @@
         <v>0</v>
       </c>
       <c r="M182">
-        <v>0.3802281368821293</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="N182">
         <v>0</v>
       </c>
       <c r="O182">
-        <v>0.7604562737642585</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="P182">
-        <v>0.7604562737642585</v>
+        <v>0</v>
       </c>
       <c r="Q182">
-        <v>0.7604562737642585</v>
+        <v>0</v>
       </c>
       <c r="R182">
-        <v>0.7604562737642585</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="S182">
-        <v>0</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="T182">
-        <v>0</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="U182">
         <v>0</v>
       </c>
       <c r="V182">
-        <v>0.7604562737642585</v>
+        <v>0</v>
       </c>
       <c r="W182">
-        <v>0.7604562737642585</v>
+        <v>0</v>
       </c>
       <c r="X182">
-        <v>1.140684410646388</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="Y182">
-        <v>0.3802281368821293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:25">
@@ -16269,73 +16269,73 @@
         <v>2022</v>
       </c>
       <c r="B183" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C183" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D183" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E183">
-        <v>0</v>
+        <v>0.353356890459364</v>
       </c>
       <c r="F183">
         <v>0</v>
       </c>
       <c r="G183">
-        <v>0</v>
+        <v>1.060070671378092</v>
       </c>
       <c r="H183">
         <v>0</v>
       </c>
       <c r="I183">
-        <v>2.083333333333333</v>
+        <v>0.353356890459364</v>
       </c>
       <c r="J183">
-        <v>4.166666666666666</v>
+        <v>1.76678445229682</v>
       </c>
       <c r="K183">
-        <v>0</v>
+        <v>0.353356890459364</v>
       </c>
       <c r="L183">
         <v>0</v>
       </c>
       <c r="M183">
-        <v>2.083333333333333</v>
+        <v>0</v>
       </c>
       <c r="N183">
-        <v>0</v>
+        <v>3.180212014134275</v>
       </c>
       <c r="O183">
-        <v>2.083333333333333</v>
+        <v>0.7067137809187279</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>0.353356890459364</v>
       </c>
       <c r="Q183">
-        <v>0</v>
+        <v>3.180212014134275</v>
       </c>
       <c r="R183">
-        <v>4.166666666666666</v>
+        <v>1.413427561837456</v>
       </c>
       <c r="S183">
-        <v>4.166666666666666</v>
+        <v>0</v>
       </c>
       <c r="T183">
-        <v>2.083333333333333</v>
+        <v>0.353356890459364</v>
       </c>
       <c r="U183">
-        <v>0</v>
+        <v>0.353356890459364</v>
       </c>
       <c r="V183">
         <v>0</v>
       </c>
       <c r="W183">
-        <v>0</v>
+        <v>0.353356890459364</v>
       </c>
       <c r="X183">
-        <v>4.166666666666666</v>
+        <v>6.36042402826855</v>
       </c>
       <c r="Y183">
         <v>0</v>
@@ -16346,73 +16346,73 @@
         <v>2022</v>
       </c>
       <c r="B184" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C184" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D184" t="s">
         <v>17</v>
       </c>
       <c r="E184">
-        <v>0.353356890459364</v>
+        <v>0</v>
       </c>
       <c r="F184">
         <v>0</v>
       </c>
       <c r="G184">
-        <v>1.060070671378092</v>
+        <v>2.631578947368421</v>
       </c>
       <c r="H184">
         <v>0</v>
       </c>
       <c r="I184">
-        <v>0.353356890459364</v>
+        <v>2.631578947368421</v>
       </c>
       <c r="J184">
-        <v>1.76678445229682</v>
+        <v>1.31578947368421</v>
       </c>
       <c r="K184">
-        <v>0.353356890459364</v>
+        <v>0</v>
       </c>
       <c r="L184">
-        <v>0</v>
+        <v>1.31578947368421</v>
       </c>
       <c r="M184">
         <v>0</v>
       </c>
       <c r="N184">
-        <v>3.180212014134275</v>
+        <v>1.31578947368421</v>
       </c>
       <c r="O184">
-        <v>0.7067137809187279</v>
+        <v>1.31578947368421</v>
       </c>
       <c r="P184">
-        <v>0.353356890459364</v>
+        <v>0</v>
       </c>
       <c r="Q184">
-        <v>3.180212014134275</v>
+        <v>1.31578947368421</v>
       </c>
       <c r="R184">
-        <v>1.413427561837456</v>
+        <v>0</v>
       </c>
       <c r="S184">
-        <v>0</v>
+        <v>3.947368421052631</v>
       </c>
       <c r="T184">
-        <v>0.353356890459364</v>
+        <v>0</v>
       </c>
       <c r="U184">
-        <v>0.353356890459364</v>
+        <v>0</v>
       </c>
       <c r="V184">
         <v>0</v>
       </c>
       <c r="W184">
-        <v>0.353356890459364</v>
+        <v>0</v>
       </c>
       <c r="X184">
-        <v>6.36042402826855</v>
+        <v>0</v>
       </c>
       <c r="Y184">
         <v>0</v>
@@ -16423,10 +16423,10 @@
         <v>2022</v>
       </c>
       <c r="B185" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C185" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D185" t="s">
         <v>17</v>
@@ -16435,46 +16435,46 @@
         <v>0</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G185">
-        <v>2.631578947368421</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="H185">
         <v>0</v>
       </c>
       <c r="I185">
-        <v>2.631578947368421</v>
+        <v>0</v>
       </c>
       <c r="J185">
-        <v>1.31578947368421</v>
+        <v>0</v>
       </c>
       <c r="K185">
         <v>0</v>
       </c>
       <c r="L185">
-        <v>1.31578947368421</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="M185">
         <v>0</v>
       </c>
       <c r="N185">
-        <v>1.31578947368421</v>
+        <v>14.85714285714286</v>
       </c>
       <c r="O185">
-        <v>1.31578947368421</v>
+        <v>0</v>
       </c>
       <c r="P185">
         <v>0</v>
       </c>
       <c r="Q185">
-        <v>1.31578947368421</v>
+        <v>0</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="S185">
-        <v>3.947368421052631</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="T185">
         <v>0</v>
@@ -16483,7 +16483,7 @@
         <v>0</v>
       </c>
       <c r="V185">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W185">
         <v>0</v>
@@ -16500,10 +16500,10 @@
         <v>2022</v>
       </c>
       <c r="B186" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C186" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D186" t="s">
         <v>17</v>
@@ -16512,10 +16512,10 @@
         <v>0</v>
       </c>
       <c r="F186">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G186">
-        <v>1.142857142857143</v>
+        <v>0.6578947368421052</v>
       </c>
       <c r="H186">
         <v>0</v>
@@ -16530,37 +16530,37 @@
         <v>0</v>
       </c>
       <c r="L186">
-        <v>1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="M186">
         <v>0</v>
       </c>
       <c r="N186">
-        <v>14.85714285714286</v>
+        <v>9.210526315789473</v>
       </c>
       <c r="O186">
         <v>0</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>1.973684210526316</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>0.6578947368421052</v>
       </c>
       <c r="R186">
-        <v>1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="S186">
-        <v>1.142857142857143</v>
+        <v>0.6578947368421052</v>
       </c>
       <c r="T186">
-        <v>0</v>
+        <v>0.6578947368421052</v>
       </c>
       <c r="U186">
         <v>0</v>
       </c>
       <c r="V186">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W186">
         <v>0</v>
@@ -16577,22 +16577,22 @@
         <v>2022</v>
       </c>
       <c r="B187" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C187" t="s">
-        <v>367</v>
+        <v>305</v>
       </c>
       <c r="D187" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>0.398406374501992</v>
       </c>
       <c r="F187">
         <v>0</v>
       </c>
       <c r="G187">
-        <v>0.6578947368421052</v>
+        <v>1.99203187250996</v>
       </c>
       <c r="H187">
         <v>0</v>
@@ -16601,49 +16601,49 @@
         <v>0</v>
       </c>
       <c r="J187">
-        <v>0</v>
+        <v>3.585657370517929</v>
       </c>
       <c r="K187">
-        <v>0</v>
+        <v>0.398406374501992</v>
       </c>
       <c r="L187">
-        <v>0</v>
+        <v>0.398406374501992</v>
       </c>
       <c r="M187">
         <v>0</v>
       </c>
       <c r="N187">
-        <v>9.210526315789473</v>
+        <v>1.195219123505976</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>0.398406374501992</v>
       </c>
       <c r="P187">
-        <v>1.973684210526316</v>
+        <v>0</v>
       </c>
       <c r="Q187">
-        <v>0.6578947368421052</v>
+        <v>0</v>
       </c>
       <c r="R187">
         <v>0</v>
       </c>
       <c r="S187">
-        <v>0.6578947368421052</v>
+        <v>0.398406374501992</v>
       </c>
       <c r="T187">
-        <v>0.6578947368421052</v>
+        <v>0.796812749003984</v>
       </c>
       <c r="U187">
-        <v>0</v>
+        <v>6.374501992031872</v>
       </c>
       <c r="V187">
-        <v>0</v>
+        <v>0.796812749003984</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>1.593625498007968</v>
       </c>
       <c r="X187">
-        <v>0</v>
+        <v>4.780876494023905</v>
       </c>
       <c r="Y187">
         <v>0</v>
@@ -16651,13 +16651,13 @@
     </row>
     <row r="188" spans="1:25">
       <c r="A188">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B188" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C188" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D188" t="s">
         <v>17</v>
@@ -16672,28 +16672,28 @@
         <v>0</v>
       </c>
       <c r="H188">
-        <v>0</v>
+        <v>0.5076142131979695</v>
       </c>
       <c r="I188">
-        <v>4.716981132075472</v>
+        <v>1.015228426395939</v>
       </c>
       <c r="J188">
-        <v>12.26415094339623</v>
+        <v>0.5076142131979695</v>
       </c>
       <c r="K188">
-        <v>0</v>
+        <v>0.5076142131979695</v>
       </c>
       <c r="L188">
-        <v>0</v>
+        <v>0.5076142131979695</v>
       </c>
       <c r="M188">
-        <v>0</v>
+        <v>1.522842639593909</v>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>5.583756345177665</v>
       </c>
       <c r="O188">
-        <v>0</v>
+        <v>0.5076142131979695</v>
       </c>
       <c r="P188">
         <v>0</v>
@@ -16702,28 +16702,28 @@
         <v>0</v>
       </c>
       <c r="R188">
-        <v>1.886792452830189</v>
+        <v>0.5076142131979695</v>
       </c>
       <c r="S188">
         <v>0</v>
       </c>
       <c r="T188">
-        <v>0</v>
+        <v>0.5076142131979695</v>
       </c>
       <c r="U188">
-        <v>0</v>
+        <v>2.538071065989848</v>
       </c>
       <c r="V188">
-        <v>0</v>
+        <v>0.5076142131979695</v>
       </c>
       <c r="W188">
-        <v>0</v>
+        <v>2.538071065989848</v>
       </c>
       <c r="X188">
-        <v>0.9433962264150944</v>
+        <v>2.030456852791878</v>
       </c>
       <c r="Y188">
-        <v>0</v>
+        <v>0.5076142131979695</v>
       </c>
     </row>
     <row r="189" spans="1:25">
@@ -16731,76 +16731,76 @@
         <v>2023</v>
       </c>
       <c r="B189" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C189" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D189" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E189">
         <v>0</v>
       </c>
       <c r="F189">
-        <v>0</v>
+        <v>5.741626794258373</v>
       </c>
       <c r="G189">
-        <v>0</v>
+        <v>5.741626794258373</v>
       </c>
       <c r="H189">
-        <v>0.5076142131979695</v>
+        <v>0</v>
       </c>
       <c r="I189">
-        <v>1.015228426395939</v>
+        <v>0</v>
       </c>
       <c r="J189">
-        <v>0.5076142131979695</v>
+        <v>0</v>
       </c>
       <c r="K189">
-        <v>0.5076142131979695</v>
+        <v>0</v>
       </c>
       <c r="L189">
-        <v>0.5076142131979695</v>
+        <v>0</v>
       </c>
       <c r="M189">
-        <v>1.522842639593909</v>
+        <v>0</v>
       </c>
       <c r="N189">
-        <v>5.583756345177665</v>
+        <v>5.741626794258373</v>
       </c>
       <c r="O189">
-        <v>0.5076142131979695</v>
+        <v>0.4784688995215311</v>
       </c>
       <c r="P189">
         <v>0</v>
       </c>
       <c r="Q189">
-        <v>0</v>
+        <v>2.870813397129186</v>
       </c>
       <c r="R189">
-        <v>0.5076142131979695</v>
+        <v>0</v>
       </c>
       <c r="S189">
         <v>0</v>
       </c>
       <c r="T189">
-        <v>0.5076142131979695</v>
+        <v>0</v>
       </c>
       <c r="U189">
-        <v>2.538071065989848</v>
+        <v>1.435406698564593</v>
       </c>
       <c r="V189">
-        <v>0.5076142131979695</v>
+        <v>1.435406698564593</v>
       </c>
       <c r="W189">
-        <v>2.538071065989848</v>
+        <v>0</v>
       </c>
       <c r="X189">
-        <v>2.030456852791878</v>
+        <v>1.913875598086124</v>
       </c>
       <c r="Y189">
-        <v>0.5076142131979695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:25">
@@ -16808,28 +16808,28 @@
         <v>2023</v>
       </c>
       <c r="B190" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C190" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D190" t="s">
         <v>11</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>0.6172839506172839</v>
       </c>
       <c r="F190">
-        <v>5.741626794258373</v>
+        <v>0</v>
       </c>
       <c r="G190">
-        <v>5.741626794258373</v>
+        <v>0.6172839506172839</v>
       </c>
       <c r="H190">
-        <v>0</v>
+        <v>1.234567901234568</v>
       </c>
       <c r="I190">
-        <v>0</v>
+        <v>3.08641975308642</v>
       </c>
       <c r="J190">
         <v>0</v>
@@ -16841,40 +16841,40 @@
         <v>0</v>
       </c>
       <c r="M190">
-        <v>0</v>
+        <v>1.234567901234568</v>
       </c>
       <c r="N190">
-        <v>5.741626794258373</v>
+        <v>3.08641975308642</v>
       </c>
       <c r="O190">
-        <v>0.4784688995215311</v>
+        <v>0.6172839506172839</v>
       </c>
       <c r="P190">
         <v>0</v>
       </c>
       <c r="Q190">
-        <v>2.870813397129186</v>
+        <v>0</v>
       </c>
       <c r="R190">
         <v>0</v>
       </c>
       <c r="S190">
-        <v>0</v>
+        <v>0.6172839506172839</v>
       </c>
       <c r="T190">
         <v>0</v>
       </c>
       <c r="U190">
-        <v>1.435406698564593</v>
+        <v>0</v>
       </c>
       <c r="V190">
-        <v>1.435406698564593</v>
+        <v>1.234567901234568</v>
       </c>
       <c r="W190">
-        <v>0</v>
+        <v>0.6172839506172839</v>
       </c>
       <c r="X190">
-        <v>1.913875598086124</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="Y190">
         <v>0</v>
@@ -16885,46 +16885,46 @@
         <v>2023</v>
       </c>
       <c r="B191" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C191" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D191" t="s">
         <v>11</v>
       </c>
       <c r="E191">
-        <v>0.6172839506172839</v>
+        <v>0.5</v>
       </c>
       <c r="F191">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G191">
-        <v>0.6172839506172839</v>
+        <v>1.5</v>
       </c>
       <c r="H191">
-        <v>1.234567901234568</v>
+        <v>0</v>
       </c>
       <c r="I191">
-        <v>3.08641975308642</v>
+        <v>2.5</v>
       </c>
       <c r="J191">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K191">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L191">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M191">
-        <v>1.234567901234568</v>
+        <v>0</v>
       </c>
       <c r="N191">
-        <v>3.08641975308642</v>
+        <v>3.5</v>
       </c>
       <c r="O191">
-        <v>0.6172839506172839</v>
+        <v>1.5</v>
       </c>
       <c r="P191">
         <v>0</v>
@@ -16933,25 +16933,25 @@
         <v>0</v>
       </c>
       <c r="R191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S191">
-        <v>0.6172839506172839</v>
+        <v>0.5</v>
       </c>
       <c r="T191">
         <v>0</v>
       </c>
       <c r="U191">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V191">
-        <v>1.234567901234568</v>
+        <v>1.5</v>
       </c>
       <c r="W191">
-        <v>0.6172839506172839</v>
+        <v>0</v>
       </c>
       <c r="X191">
-        <v>1.851851851851852</v>
+        <v>1.5</v>
       </c>
       <c r="Y191">
         <v>0</v>
@@ -16962,73 +16962,73 @@
         <v>2023</v>
       </c>
       <c r="B192" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C192" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D192" t="s">
         <v>11</v>
       </c>
       <c r="E192">
-        <v>0.5</v>
+        <v>1.376146788990826</v>
       </c>
       <c r="F192">
-        <v>3</v>
+        <v>2.293577981651376</v>
       </c>
       <c r="G192">
-        <v>1.5</v>
+        <v>0.4587155963302753</v>
       </c>
       <c r="H192">
         <v>0</v>
       </c>
       <c r="I192">
-        <v>2.5</v>
+        <v>1.834862385321101</v>
       </c>
       <c r="J192">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K192">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L192">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M192">
-        <v>0</v>
+        <v>0.4587155963302753</v>
       </c>
       <c r="N192">
-        <v>3.5</v>
+        <v>0.9174311926605505</v>
       </c>
       <c r="O192">
-        <v>1.5</v>
+        <v>1.834862385321101</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>0.9174311926605505</v>
       </c>
       <c r="Q192">
         <v>0</v>
       </c>
       <c r="R192">
-        <v>1</v>
+        <v>0.9174311926605505</v>
       </c>
       <c r="S192">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T192">
         <v>0</v>
       </c>
       <c r="U192">
-        <v>0.5</v>
+        <v>0.4587155963302753</v>
       </c>
       <c r="V192">
-        <v>1.5</v>
+        <v>0.4587155963302753</v>
       </c>
       <c r="W192">
-        <v>0</v>
+        <v>0.9174311926605505</v>
       </c>
       <c r="X192">
-        <v>1.5</v>
+        <v>1.376146788990826</v>
       </c>
       <c r="Y192">
         <v>0</v>
@@ -17039,76 +17039,76 @@
         <v>2023</v>
       </c>
       <c r="B193" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C193" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D193" t="s">
         <v>11</v>
       </c>
       <c r="E193">
-        <v>1.376146788990826</v>
+        <v>1.463414634146342</v>
       </c>
       <c r="F193">
-        <v>2.293577981651376</v>
+        <v>2.926829268292683</v>
       </c>
       <c r="G193">
-        <v>0.4587155963302753</v>
+        <v>1.463414634146342</v>
       </c>
       <c r="H193">
         <v>0</v>
       </c>
       <c r="I193">
-        <v>1.834862385321101</v>
+        <v>2.926829268292683</v>
       </c>
       <c r="J193">
         <v>0</v>
       </c>
       <c r="K193">
-        <v>0</v>
+        <v>1.463414634146342</v>
       </c>
       <c r="L193">
         <v>0</v>
       </c>
       <c r="M193">
-        <v>0.4587155963302753</v>
+        <v>0</v>
       </c>
       <c r="N193">
-        <v>0.9174311926605505</v>
+        <v>6.829268292682928</v>
       </c>
       <c r="O193">
-        <v>1.834862385321101</v>
+        <v>0</v>
       </c>
       <c r="P193">
-        <v>0.9174311926605505</v>
+        <v>0.975609756097561</v>
       </c>
       <c r="Q193">
         <v>0</v>
       </c>
       <c r="R193">
-        <v>0.9174311926605505</v>
+        <v>5.365853658536586</v>
       </c>
       <c r="S193">
         <v>0</v>
       </c>
       <c r="T193">
-        <v>0</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="U193">
-        <v>0.4587155963302753</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="V193">
-        <v>0.4587155963302753</v>
+        <v>1.463414634146342</v>
       </c>
       <c r="W193">
-        <v>0.9174311926605505</v>
+        <v>0</v>
       </c>
       <c r="X193">
-        <v>1.376146788990826</v>
+        <v>2.439024390243902</v>
       </c>
       <c r="Y193">
-        <v>0</v>
+        <v>1.951219512195122</v>
       </c>
     </row>
     <row r="194" spans="1:25">
@@ -17116,76 +17116,76 @@
         <v>2023</v>
       </c>
       <c r="B194" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C194" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D194" t="s">
         <v>11</v>
       </c>
       <c r="E194">
-        <v>1.463414634146342</v>
+        <v>0.2816901408450704</v>
       </c>
       <c r="F194">
-        <v>2.926829268292683</v>
+        <v>0</v>
       </c>
       <c r="G194">
-        <v>1.463414634146342</v>
+        <v>0.5633802816901409</v>
       </c>
       <c r="H194">
-        <v>0</v>
+        <v>0.5633802816901409</v>
       </c>
       <c r="I194">
-        <v>2.926829268292683</v>
+        <v>0.8450704225352111</v>
       </c>
       <c r="J194">
         <v>0</v>
       </c>
       <c r="K194">
-        <v>1.463414634146342</v>
+        <v>0.2816901408450704</v>
       </c>
       <c r="L194">
-        <v>0</v>
+        <v>0.2816901408450704</v>
       </c>
       <c r="M194">
-        <v>0</v>
+        <v>1.690140845070422</v>
       </c>
       <c r="N194">
-        <v>6.829268292682928</v>
+        <v>2.535211267605634</v>
       </c>
       <c r="O194">
-        <v>0</v>
+        <v>0.2816901408450704</v>
       </c>
       <c r="P194">
-        <v>0.975609756097561</v>
+        <v>0</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>0.2816901408450704</v>
       </c>
       <c r="R194">
-        <v>5.365853658536586</v>
+        <v>0.8450704225352111</v>
       </c>
       <c r="S194">
         <v>0</v>
       </c>
       <c r="T194">
-        <v>0.4878048780487805</v>
+        <v>0.2816901408450704</v>
       </c>
       <c r="U194">
-        <v>0.4878048780487805</v>
+        <v>3.098591549295775</v>
       </c>
       <c r="V194">
-        <v>1.463414634146342</v>
+        <v>0.2816901408450704</v>
       </c>
       <c r="W194">
-        <v>0</v>
+        <v>0.5633802816901409</v>
       </c>
       <c r="X194">
-        <v>2.439024390243902</v>
+        <v>0.8450704225352111</v>
       </c>
       <c r="Y194">
-        <v>1.951219512195122</v>
+        <v>0.2816901408450704</v>
       </c>
     </row>
     <row r="195" spans="1:25">
@@ -17193,76 +17193,76 @@
         <v>2023</v>
       </c>
       <c r="B195" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C195" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D195" t="s">
         <v>11</v>
       </c>
       <c r="E195">
-        <v>0.2816901408450704</v>
+        <v>0</v>
       </c>
       <c r="F195">
-        <v>0</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="G195">
-        <v>0.5633802816901409</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="H195">
-        <v>0.5633802816901409</v>
+        <v>0</v>
       </c>
       <c r="I195">
-        <v>0.8450704225352111</v>
+        <v>0</v>
       </c>
       <c r="J195">
         <v>0</v>
       </c>
       <c r="K195">
-        <v>0.2816901408450704</v>
+        <v>0</v>
       </c>
       <c r="L195">
-        <v>0.2816901408450704</v>
+        <v>0</v>
       </c>
       <c r="M195">
-        <v>1.690140845070422</v>
+        <v>0</v>
       </c>
       <c r="N195">
-        <v>2.535211267605634</v>
+        <v>4.761904761904762</v>
       </c>
       <c r="O195">
-        <v>0.2816901408450704</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="Q195">
-        <v>0.2816901408450704</v>
+        <v>0</v>
       </c>
       <c r="R195">
-        <v>0.8450704225352111</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="S195">
         <v>0</v>
       </c>
       <c r="T195">
-        <v>0.2816901408450704</v>
+        <v>0</v>
       </c>
       <c r="U195">
-        <v>3.098591549295775</v>
+        <v>0</v>
       </c>
       <c r="V195">
-        <v>0.2816901408450704</v>
+        <v>3.80952380952381</v>
       </c>
       <c r="W195">
-        <v>0.5633802816901409</v>
+        <v>1.904761904761905</v>
       </c>
       <c r="X195">
-        <v>0.8450704225352111</v>
+        <v>0.9523809523809524</v>
       </c>
       <c r="Y195">
-        <v>0.2816901408450704</v>
+        <v>0.4761904761904762</v>
       </c>
     </row>
     <row r="196" spans="1:25">
@@ -17270,76 +17270,76 @@
         <v>2023</v>
       </c>
       <c r="B196" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C196" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D196" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E196">
-        <v>0</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="F196">
-        <v>1.428571428571429</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="G196">
-        <v>4.285714285714286</v>
+        <v>8.709677419354838</v>
       </c>
       <c r="H196">
-        <v>0</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="I196">
         <v>0</v>
       </c>
       <c r="J196">
-        <v>0</v>
+        <v>1.612903225806452</v>
       </c>
       <c r="K196">
-        <v>0</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="L196">
-        <v>0</v>
+        <v>1.290322580645161</v>
       </c>
       <c r="M196">
-        <v>0</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="N196">
-        <v>4.761904761904762</v>
+        <v>8.709677419354838</v>
       </c>
       <c r="O196">
-        <v>2.857142857142857</v>
+        <v>0</v>
       </c>
       <c r="P196">
-        <v>0.4761904761904762</v>
+        <v>0</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>1.935483870967742</v>
       </c>
       <c r="R196">
-        <v>6.666666666666667</v>
+        <v>2.580645161290323</v>
       </c>
       <c r="S196">
         <v>0</v>
       </c>
       <c r="T196">
-        <v>0</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="U196">
         <v>0</v>
       </c>
       <c r="V196">
-        <v>3.80952380952381</v>
+        <v>2.903225806451613</v>
       </c>
       <c r="W196">
-        <v>1.904761904761905</v>
+        <v>0</v>
       </c>
       <c r="X196">
-        <v>0.9523809523809524</v>
+        <v>0</v>
       </c>
       <c r="Y196">
-        <v>0.4761904761904762</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:25">
@@ -17347,43 +17347,43 @@
         <v>2023</v>
       </c>
       <c r="B197" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C197" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D197" t="s">
         <v>17</v>
       </c>
       <c r="E197">
-        <v>0.6451612903225806</v>
+        <v>0</v>
       </c>
       <c r="F197">
-        <v>0.3225806451612903</v>
+        <v>7.065217391304348</v>
       </c>
       <c r="G197">
-        <v>8.709677419354838</v>
+        <v>0</v>
       </c>
       <c r="H197">
-        <v>0.3225806451612903</v>
+        <v>0</v>
       </c>
       <c r="I197">
-        <v>0</v>
+        <v>1.630434782608696</v>
       </c>
       <c r="J197">
-        <v>1.612903225806452</v>
+        <v>1.08695652173913</v>
       </c>
       <c r="K197">
-        <v>0.3225806451612903</v>
+        <v>1.08695652173913</v>
       </c>
       <c r="L197">
-        <v>1.290322580645161</v>
+        <v>0</v>
       </c>
       <c r="M197">
-        <v>0.3225806451612903</v>
+        <v>1.08695652173913</v>
       </c>
       <c r="N197">
-        <v>8.709677419354838</v>
+        <v>11.41304347826087</v>
       </c>
       <c r="O197">
         <v>0</v>
@@ -17392,28 +17392,28 @@
         <v>0</v>
       </c>
       <c r="Q197">
-        <v>1.935483870967742</v>
+        <v>0</v>
       </c>
       <c r="R197">
-        <v>2.580645161290323</v>
+        <v>1.630434782608696</v>
       </c>
       <c r="S197">
         <v>0</v>
       </c>
       <c r="T197">
-        <v>0.6451612903225806</v>
+        <v>0</v>
       </c>
       <c r="U197">
         <v>0</v>
       </c>
       <c r="V197">
-        <v>2.903225806451613</v>
+        <v>0.5434782608695652</v>
       </c>
       <c r="W197">
         <v>0</v>
       </c>
       <c r="X197">
-        <v>0</v>
+        <v>1.08695652173913</v>
       </c>
       <c r="Y197">
         <v>0</v>
@@ -17424,19 +17424,19 @@
         <v>2023</v>
       </c>
       <c r="B198" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C198" t="s">
-        <v>388</v>
+        <v>159</v>
       </c>
       <c r="D198" t="s">
         <v>17</v>
       </c>
       <c r="E198">
-        <v>0</v>
+        <v>0.7462686567164178</v>
       </c>
       <c r="F198">
-        <v>7.065217391304348</v>
+        <v>0</v>
       </c>
       <c r="G198">
         <v>0</v>
@@ -17445,22 +17445,22 @@
         <v>0</v>
       </c>
       <c r="I198">
-        <v>1.630434782608696</v>
+        <v>0.7462686567164178</v>
       </c>
       <c r="J198">
-        <v>1.08695652173913</v>
+        <v>0</v>
       </c>
       <c r="K198">
-        <v>1.08695652173913</v>
+        <v>0.7462686567164178</v>
       </c>
       <c r="L198">
         <v>0</v>
       </c>
       <c r="M198">
-        <v>1.08695652173913</v>
+        <v>2.238805970149254</v>
       </c>
       <c r="N198">
-        <v>11.41304347826087</v>
+        <v>5.223880597014925</v>
       </c>
       <c r="O198">
         <v>0</v>
@@ -17472,25 +17472,25 @@
         <v>0</v>
       </c>
       <c r="R198">
-        <v>1.630434782608696</v>
+        <v>0</v>
       </c>
       <c r="S198">
-        <v>0</v>
+        <v>0.7462686567164178</v>
       </c>
       <c r="T198">
         <v>0</v>
       </c>
       <c r="U198">
-        <v>0</v>
+        <v>0.7462686567164178</v>
       </c>
       <c r="V198">
-        <v>0.5434782608695652</v>
+        <v>0.7462686567164178</v>
       </c>
       <c r="W198">
-        <v>0</v>
+        <v>1.492537313432836</v>
       </c>
       <c r="X198">
-        <v>1.08695652173913</v>
+        <v>0.7462686567164178</v>
       </c>
       <c r="Y198">
         <v>0</v>
@@ -17501,7 +17501,7 @@
         <v>2023</v>
       </c>
       <c r="B199" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C199" t="s">
         <v>159</v>
@@ -17510,37 +17510,37 @@
         <v>17</v>
       </c>
       <c r="E199">
-        <v>0.7462686567164178</v>
+        <v>0</v>
       </c>
       <c r="F199">
         <v>0</v>
       </c>
       <c r="G199">
-        <v>0</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="H199">
         <v>0</v>
       </c>
       <c r="I199">
-        <v>0.7462686567164178</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="J199">
         <v>0</v>
       </c>
       <c r="K199">
-        <v>0.7462686567164178</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="L199">
         <v>0</v>
       </c>
       <c r="M199">
-        <v>2.238805970149254</v>
+        <v>0</v>
       </c>
       <c r="N199">
-        <v>5.223880597014925</v>
+        <v>13.57142857142857</v>
       </c>
       <c r="O199">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="P199">
         <v>0</v>
@@ -17549,25 +17549,25 @@
         <v>0</v>
       </c>
       <c r="R199">
-        <v>0</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="S199">
-        <v>0.7462686567164178</v>
+        <v>0</v>
       </c>
       <c r="T199">
         <v>0</v>
       </c>
       <c r="U199">
-        <v>0.7462686567164178</v>
+        <v>0</v>
       </c>
       <c r="V199">
-        <v>0.7462686567164178</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="W199">
-        <v>1.492537313432836</v>
+        <v>0</v>
       </c>
       <c r="X199">
-        <v>0.7462686567164178</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="Y199">
         <v>0</v>
@@ -17578,10 +17578,10 @@
         <v>2023</v>
       </c>
       <c r="B200" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C200" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="D200" t="s">
         <v>17</v>
@@ -17590,22 +17590,22 @@
         <v>0</v>
       </c>
       <c r="F200">
-        <v>0</v>
+        <v>5.072463768115942</v>
       </c>
       <c r="G200">
-        <v>1.428571428571429</v>
+        <v>1.449275362318841</v>
       </c>
       <c r="H200">
         <v>0</v>
       </c>
       <c r="I200">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="J200">
         <v>0</v>
       </c>
       <c r="K200">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="L200">
         <v>0</v>
@@ -17614,10 +17614,10 @@
         <v>0</v>
       </c>
       <c r="N200">
-        <v>13.57142857142857</v>
+        <v>11.59420289855072</v>
       </c>
       <c r="O200">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="P200">
         <v>0</v>
@@ -17626,7 +17626,7 @@
         <v>0</v>
       </c>
       <c r="R200">
-        <v>4.285714285714286</v>
+        <v>0</v>
       </c>
       <c r="S200">
         <v>0</v>
@@ -17638,13 +17638,13 @@
         <v>0</v>
       </c>
       <c r="V200">
-        <v>1.428571428571429</v>
+        <v>3.623188405797102</v>
       </c>
       <c r="W200">
         <v>0</v>
       </c>
       <c r="X200">
-        <v>1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="Y200">
         <v>0</v>
@@ -17652,34 +17652,34 @@
     </row>
     <row r="201" spans="1:25">
       <c r="A201">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B201" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C201" t="s">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="D201" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E201">
         <v>0</v>
       </c>
       <c r="F201">
-        <v>5.072463768115942</v>
+        <v>0</v>
       </c>
       <c r="G201">
-        <v>1.449275362318841</v>
+        <v>0</v>
       </c>
       <c r="H201">
         <v>0</v>
       </c>
       <c r="I201">
-        <v>0</v>
+        <v>2.631578947368421</v>
       </c>
       <c r="J201">
-        <v>0</v>
+        <v>1.754385964912281</v>
       </c>
       <c r="K201">
         <v>0</v>
@@ -17691,10 +17691,10 @@
         <v>0</v>
       </c>
       <c r="N201">
-        <v>11.59420289855072</v>
+        <v>3.508771929824561</v>
       </c>
       <c r="O201">
-        <v>0</v>
+        <v>0.8771929824561403</v>
       </c>
       <c r="P201">
         <v>0</v>
@@ -17703,7 +17703,7 @@
         <v>0</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>6.140350877192982</v>
       </c>
       <c r="S201">
         <v>0</v>
@@ -17712,10 +17712,10 @@
         <v>0</v>
       </c>
       <c r="U201">
-        <v>0</v>
+        <v>1.754385964912281</v>
       </c>
       <c r="V201">
-        <v>3.623188405797102</v>
+        <v>0</v>
       </c>
       <c r="W201">
         <v>0</v>
@@ -17732,10 +17732,10 @@
         <v>2024</v>
       </c>
       <c r="B202" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C202" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D202" t="s">
         <v>11</v>
@@ -17744,61 +17744,61 @@
         <v>0</v>
       </c>
       <c r="F202">
-        <v>0</v>
+        <v>3.370786516853932</v>
       </c>
       <c r="G202">
-        <v>0</v>
+        <v>1.123595505617978</v>
       </c>
       <c r="H202">
         <v>0</v>
       </c>
       <c r="I202">
-        <v>2.631578947368421</v>
+        <v>0</v>
       </c>
       <c r="J202">
-        <v>1.754385964912281</v>
+        <v>0</v>
       </c>
       <c r="K202">
-        <v>0</v>
+        <v>0.5617977528089888</v>
       </c>
       <c r="L202">
-        <v>0</v>
+        <v>0.5617977528089888</v>
       </c>
       <c r="M202">
-        <v>0</v>
+        <v>1.123595505617978</v>
       </c>
       <c r="N202">
-        <v>3.508771929824561</v>
+        <v>4.49438202247191</v>
       </c>
       <c r="O202">
-        <v>0.8771929824561403</v>
+        <v>0</v>
       </c>
       <c r="P202">
         <v>0</v>
       </c>
       <c r="Q202">
-        <v>0</v>
+        <v>0.5617977528089888</v>
       </c>
       <c r="R202">
-        <v>6.140350877192982</v>
+        <v>3.932584269662921</v>
       </c>
       <c r="S202">
-        <v>0</v>
+        <v>0.5617977528089888</v>
       </c>
       <c r="T202">
         <v>0</v>
       </c>
       <c r="U202">
-        <v>1.754385964912281</v>
+        <v>0.5617977528089888</v>
       </c>
       <c r="V202">
-        <v>0</v>
+        <v>1.123595505617978</v>
       </c>
       <c r="W202">
-        <v>0</v>
+        <v>0.5617977528089888</v>
       </c>
       <c r="X202">
-        <v>0</v>
+        <v>4.49438202247191</v>
       </c>
       <c r="Y202">
         <v>0</v>
@@ -17809,10 +17809,10 @@
         <v>2024</v>
       </c>
       <c r="B203" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C203" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D203" t="s">
         <v>11</v>
@@ -17821,64 +17821,64 @@
         <v>0</v>
       </c>
       <c r="F203">
-        <v>3.370786516853932</v>
+        <v>0.4608294930875576</v>
       </c>
       <c r="G203">
-        <v>1.123595505617978</v>
+        <v>1.84331797235023</v>
       </c>
       <c r="H203">
         <v>0</v>
       </c>
       <c r="I203">
-        <v>0</v>
+        <v>1.382488479262673</v>
       </c>
       <c r="J203">
         <v>0</v>
       </c>
       <c r="K203">
-        <v>0.5617977528089888</v>
+        <v>0</v>
       </c>
       <c r="L203">
-        <v>0.5617977528089888</v>
+        <v>0</v>
       </c>
       <c r="M203">
-        <v>1.123595505617978</v>
+        <v>0.4608294930875576</v>
       </c>
       <c r="N203">
-        <v>4.49438202247191</v>
+        <v>7.373271889400922</v>
       </c>
       <c r="O203">
-        <v>0</v>
+        <v>0.9216589861751152</v>
       </c>
       <c r="P203">
-        <v>0</v>
+        <v>1.382488479262673</v>
       </c>
       <c r="Q203">
-        <v>0.5617977528089888</v>
+        <v>1.382488479262673</v>
       </c>
       <c r="R203">
-        <v>3.932584269662921</v>
+        <v>4.608294930875577</v>
       </c>
       <c r="S203">
-        <v>0.5617977528089888</v>
+        <v>0</v>
       </c>
       <c r="T203">
         <v>0</v>
       </c>
       <c r="U203">
-        <v>0.5617977528089888</v>
+        <v>1.382488479262673</v>
       </c>
       <c r="V203">
-        <v>1.123595505617978</v>
+        <v>1.382488479262673</v>
       </c>
       <c r="W203">
-        <v>0.5617977528089888</v>
+        <v>2.764976958525346</v>
       </c>
       <c r="X203">
-        <v>4.49438202247191</v>
+        <v>1.84331797235023</v>
       </c>
       <c r="Y203">
-        <v>0</v>
+        <v>0.4608294930875576</v>
       </c>
     </row>
     <row r="204" spans="1:25">
@@ -17886,28 +17886,28 @@
         <v>2024</v>
       </c>
       <c r="B204" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C204" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
       <c r="D204" t="s">
         <v>11</v>
       </c>
       <c r="E204">
-        <v>0</v>
+        <v>0.5586592178770949</v>
       </c>
       <c r="F204">
-        <v>0.4608294930875576</v>
+        <v>0</v>
       </c>
       <c r="G204">
-        <v>1.84331797235023</v>
+        <v>2.23463687150838</v>
       </c>
       <c r="H204">
         <v>0</v>
       </c>
       <c r="I204">
-        <v>1.382488479262673</v>
+        <v>0.5586592178770949</v>
       </c>
       <c r="J204">
         <v>0</v>
@@ -17916,25 +17916,25 @@
         <v>0</v>
       </c>
       <c r="L204">
-        <v>0</v>
+        <v>1.11731843575419</v>
       </c>
       <c r="M204">
-        <v>0.4608294930875576</v>
+        <v>0</v>
       </c>
       <c r="N204">
-        <v>7.373271889400922</v>
+        <v>0.5586592178770949</v>
       </c>
       <c r="O204">
-        <v>0.9216589861751152</v>
+        <v>0</v>
       </c>
       <c r="P204">
-        <v>1.382488479262673</v>
+        <v>0</v>
       </c>
       <c r="Q204">
-        <v>1.382488479262673</v>
+        <v>0</v>
       </c>
       <c r="R204">
-        <v>4.608294930875577</v>
+        <v>0</v>
       </c>
       <c r="S204">
         <v>0</v>
@@ -17943,19 +17943,19 @@
         <v>0</v>
       </c>
       <c r="U204">
-        <v>1.382488479262673</v>
+        <v>0</v>
       </c>
       <c r="V204">
-        <v>1.382488479262673</v>
+        <v>1.11731843575419</v>
       </c>
       <c r="W204">
-        <v>2.764976958525346</v>
+        <v>0</v>
       </c>
       <c r="X204">
-        <v>1.84331797235023</v>
+        <v>0.5586592178770949</v>
       </c>
       <c r="Y204">
-        <v>0.4608294930875576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:25">
@@ -17963,55 +17963,55 @@
         <v>2024</v>
       </c>
       <c r="B205" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C205" t="s">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="D205" t="s">
         <v>11</v>
       </c>
       <c r="E205">
-        <v>0.5586592178770949</v>
+        <v>2.352941176470588</v>
       </c>
       <c r="F205">
-        <v>0</v>
+        <v>1.764705882352941</v>
       </c>
       <c r="G205">
-        <v>2.23463687150838</v>
+        <v>2.352941176470588</v>
       </c>
       <c r="H205">
         <v>0</v>
       </c>
       <c r="I205">
-        <v>0.5586592178770949</v>
+        <v>2.941176470588235</v>
       </c>
       <c r="J205">
-        <v>0</v>
+        <v>2.352941176470588</v>
       </c>
       <c r="K205">
-        <v>0</v>
+        <v>1.764705882352941</v>
       </c>
       <c r="L205">
-        <v>1.11731843575419</v>
+        <v>0</v>
       </c>
       <c r="M205">
-        <v>0</v>
+        <v>1.176470588235294</v>
       </c>
       <c r="N205">
-        <v>0.5586592178770949</v>
+        <v>3.529411764705882</v>
       </c>
       <c r="O205">
-        <v>0</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P205">
-        <v>0</v>
+        <v>1.176470588235294</v>
       </c>
       <c r="Q205">
-        <v>0</v>
+        <v>1.176470588235294</v>
       </c>
       <c r="R205">
-        <v>0</v>
+        <v>2.352941176470588</v>
       </c>
       <c r="S205">
         <v>0</v>
@@ -18023,13 +18023,13 @@
         <v>0</v>
       </c>
       <c r="V205">
-        <v>1.11731843575419</v>
+        <v>0</v>
       </c>
       <c r="W205">
         <v>0</v>
       </c>
       <c r="X205">
-        <v>0.5586592178770949</v>
+        <v>2.941176470588235</v>
       </c>
       <c r="Y205">
         <v>0</v>
@@ -18040,73 +18040,73 @@
         <v>2024</v>
       </c>
       <c r="B206" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C206" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D206" t="s">
         <v>11</v>
       </c>
       <c r="E206">
-        <v>2.352941176470588</v>
+        <v>0</v>
       </c>
       <c r="F206">
-        <v>1.764705882352941</v>
+        <v>0</v>
       </c>
       <c r="G206">
-        <v>2.352941176470588</v>
+        <v>1.96078431372549</v>
       </c>
       <c r="H206">
         <v>0</v>
       </c>
       <c r="I206">
-        <v>2.941176470588235</v>
+        <v>0</v>
       </c>
       <c r="J206">
-        <v>2.352941176470588</v>
+        <v>0</v>
       </c>
       <c r="K206">
-        <v>1.764705882352941</v>
+        <v>0</v>
       </c>
       <c r="L206">
         <v>0</v>
       </c>
       <c r="M206">
-        <v>1.176470588235294</v>
+        <v>0.6535947712418301</v>
       </c>
       <c r="N206">
-        <v>3.529411764705882</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="O206">
-        <v>0.5882352941176471</v>
+        <v>0</v>
       </c>
       <c r="P206">
-        <v>1.176470588235294</v>
+        <v>0.6535947712418301</v>
       </c>
       <c r="Q206">
-        <v>1.176470588235294</v>
+        <v>3.267973856209151</v>
       </c>
       <c r="R206">
-        <v>2.352941176470588</v>
+        <v>1.30718954248366</v>
       </c>
       <c r="S206">
         <v>0</v>
       </c>
       <c r="T206">
-        <v>0</v>
+        <v>0.6535947712418301</v>
       </c>
       <c r="U206">
         <v>0</v>
       </c>
       <c r="V206">
-        <v>0</v>
+        <v>1.30718954248366</v>
       </c>
       <c r="W206">
         <v>0</v>
       </c>
       <c r="X206">
-        <v>2.941176470588235</v>
+        <v>4.57516339869281</v>
       </c>
       <c r="Y206">
         <v>0</v>
@@ -18117,10 +18117,10 @@
         <v>2024</v>
       </c>
       <c r="B207" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C207" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D207" t="s">
         <v>11</v>
@@ -18129,61 +18129,61 @@
         <v>0</v>
       </c>
       <c r="F207">
-        <v>0</v>
+        <v>0.4830917874396135</v>
       </c>
       <c r="G207">
-        <v>1.96078431372549</v>
+        <v>0</v>
       </c>
       <c r="H207">
         <v>0</v>
       </c>
       <c r="I207">
-        <v>0</v>
+        <v>0.4830917874396135</v>
       </c>
       <c r="J207">
-        <v>0</v>
+        <v>0.4830917874396135</v>
       </c>
       <c r="K207">
-        <v>0</v>
+        <v>0.4830917874396135</v>
       </c>
       <c r="L207">
-        <v>0</v>
+        <v>1.932367149758454</v>
       </c>
       <c r="M207">
-        <v>0.6535947712418301</v>
+        <v>0</v>
       </c>
       <c r="N207">
-        <v>5.88235294117647</v>
+        <v>0.4830917874396135</v>
       </c>
       <c r="O207">
-        <v>0</v>
+        <v>0.966183574879227</v>
       </c>
       <c r="P207">
-        <v>0.6535947712418301</v>
+        <v>0</v>
       </c>
       <c r="Q207">
-        <v>3.267973856209151</v>
+        <v>0</v>
       </c>
       <c r="R207">
-        <v>1.30718954248366</v>
+        <v>0</v>
       </c>
       <c r="S207">
         <v>0</v>
       </c>
       <c r="T207">
-        <v>0.6535947712418301</v>
+        <v>0</v>
       </c>
       <c r="U207">
-        <v>0</v>
+        <v>3.381642512077295</v>
       </c>
       <c r="V207">
-        <v>1.30718954248366</v>
+        <v>2.898550724637681</v>
       </c>
       <c r="W207">
         <v>0</v>
       </c>
       <c r="X207">
-        <v>4.57516339869281</v>
+        <v>2.898550724637681</v>
       </c>
       <c r="Y207">
         <v>0</v>
@@ -18194,10 +18194,10 @@
         <v>2024</v>
       </c>
       <c r="B208" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C208" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D208" t="s">
         <v>11</v>
@@ -18206,55 +18206,55 @@
         <v>0</v>
       </c>
       <c r="F208">
-        <v>0.4830917874396135</v>
+        <v>2.173913043478261</v>
       </c>
       <c r="G208">
-        <v>0</v>
+        <v>1.932367149758454</v>
       </c>
       <c r="H208">
-        <v>0</v>
+        <v>0.2415458937198068</v>
       </c>
       <c r="I208">
         <v>0.4830917874396135</v>
       </c>
       <c r="J208">
-        <v>0.4830917874396135</v>
+        <v>1.690821256038647</v>
       </c>
       <c r="K208">
         <v>0.4830917874396135</v>
       </c>
       <c r="L208">
-        <v>1.932367149758454</v>
+        <v>0</v>
       </c>
       <c r="M208">
-        <v>0</v>
+        <v>0.2415458937198068</v>
       </c>
       <c r="N208">
-        <v>0.4830917874396135</v>
+        <v>9.178743961352657</v>
       </c>
       <c r="O208">
         <v>0.966183574879227</v>
       </c>
       <c r="P208">
-        <v>0</v>
+        <v>0.4830917874396135</v>
       </c>
       <c r="Q208">
         <v>0</v>
       </c>
       <c r="R208">
-        <v>0</v>
+        <v>1.690821256038647</v>
       </c>
       <c r="S208">
-        <v>0</v>
+        <v>0.2415458937198068</v>
       </c>
       <c r="T208">
-        <v>0</v>
+        <v>1.207729468599034</v>
       </c>
       <c r="U208">
-        <v>3.381642512077295</v>
+        <v>0</v>
       </c>
       <c r="V208">
-        <v>2.898550724637681</v>
+        <v>0.7246376811594203</v>
       </c>
       <c r="W208">
         <v>0</v>
@@ -18263,7 +18263,7 @@
         <v>2.898550724637681</v>
       </c>
       <c r="Y208">
-        <v>0</v>
+        <v>0.7246376811594203</v>
       </c>
     </row>
     <row r="209" spans="1:25">
@@ -18271,76 +18271,76 @@
         <v>2024</v>
       </c>
       <c r="B209" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C209" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D209" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E209">
         <v>0</v>
       </c>
       <c r="F209">
-        <v>2.173913043478261</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="G209">
-        <v>1.932367149758454</v>
+        <v>3.428571428571429</v>
       </c>
       <c r="H209">
-        <v>0.2415458937198068</v>
+        <v>0</v>
       </c>
       <c r="I209">
-        <v>0.4830917874396135</v>
+        <v>0</v>
       </c>
       <c r="J209">
-        <v>1.690821256038647</v>
+        <v>0</v>
       </c>
       <c r="K209">
-        <v>0.4830917874396135</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="L209">
         <v>0</v>
       </c>
       <c r="M209">
-        <v>0.2415458937198068</v>
+        <v>0</v>
       </c>
       <c r="N209">
-        <v>9.178743961352657</v>
+        <v>4</v>
       </c>
       <c r="O209">
-        <v>0.966183574879227</v>
+        <v>0</v>
       </c>
       <c r="P209">
-        <v>0.4830917874396135</v>
+        <v>0</v>
       </c>
       <c r="Q209">
         <v>0</v>
       </c>
       <c r="R209">
-        <v>1.690821256038647</v>
+        <v>10.85714285714286</v>
       </c>
       <c r="S209">
-        <v>0.2415458937198068</v>
+        <v>0</v>
       </c>
       <c r="T209">
-        <v>1.207729468599034</v>
+        <v>0</v>
       </c>
       <c r="U209">
         <v>0</v>
       </c>
       <c r="V209">
-        <v>0.7246376811594203</v>
+        <v>4</v>
       </c>
       <c r="W209">
         <v>0</v>
       </c>
       <c r="X209">
-        <v>2.898550724637681</v>
+        <v>0</v>
       </c>
       <c r="Y209">
-        <v>0.7246376811594203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:25">
@@ -18348,10 +18348,10 @@
         <v>2024</v>
       </c>
       <c r="B210" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C210" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D210" t="s">
         <v>17</v>
@@ -18360,22 +18360,22 @@
         <v>0</v>
       </c>
       <c r="F210">
-        <v>1.714285714285714</v>
+        <v>1.652892561983471</v>
       </c>
       <c r="G210">
-        <v>3.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="H210">
         <v>0</v>
       </c>
       <c r="I210">
-        <v>0</v>
+        <v>0.4132231404958678</v>
       </c>
       <c r="J210">
         <v>0</v>
       </c>
       <c r="K210">
-        <v>0.5714285714285714</v>
+        <v>0.4132231404958678</v>
       </c>
       <c r="L210">
         <v>0</v>
@@ -18384,7 +18384,7 @@
         <v>0</v>
       </c>
       <c r="N210">
-        <v>4</v>
+        <v>1.652892561983471</v>
       </c>
       <c r="O210">
         <v>0</v>
@@ -18393,10 +18393,10 @@
         <v>0</v>
       </c>
       <c r="Q210">
-        <v>0</v>
+        <v>1.652892561983471</v>
       </c>
       <c r="R210">
-        <v>10.85714285714286</v>
+        <v>0</v>
       </c>
       <c r="S210">
         <v>0</v>
@@ -18405,16 +18405,16 @@
         <v>0</v>
       </c>
       <c r="U210">
-        <v>0</v>
+        <v>2.066115702479339</v>
       </c>
       <c r="V210">
-        <v>4</v>
+        <v>3.305785123966942</v>
       </c>
       <c r="W210">
         <v>0</v>
       </c>
       <c r="X210">
-        <v>0</v>
+        <v>0.8264462809917356</v>
       </c>
       <c r="Y210">
         <v>0</v>
@@ -18425,43 +18425,43 @@
         <v>2024</v>
       </c>
       <c r="B211" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C211" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D211" t="s">
         <v>17</v>
       </c>
       <c r="E211">
-        <v>0</v>
+        <v>1.973684210526316</v>
       </c>
       <c r="F211">
-        <v>1.652892561983471</v>
+        <v>0</v>
       </c>
       <c r="G211">
-        <v>0</v>
+        <v>0.6578947368421052</v>
       </c>
       <c r="H211">
         <v>0</v>
       </c>
       <c r="I211">
-        <v>0.4132231404958678</v>
+        <v>2.631578947368421</v>
       </c>
       <c r="J211">
         <v>0</v>
       </c>
       <c r="K211">
-        <v>0.4132231404958678</v>
+        <v>0</v>
       </c>
       <c r="L211">
         <v>0</v>
       </c>
       <c r="M211">
-        <v>0</v>
+        <v>2.631578947368421</v>
       </c>
       <c r="N211">
-        <v>1.652892561983471</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="O211">
         <v>0</v>
@@ -18470,10 +18470,10 @@
         <v>0</v>
       </c>
       <c r="Q211">
-        <v>1.652892561983471</v>
+        <v>0</v>
       </c>
       <c r="R211">
-        <v>0</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="S211">
         <v>0</v>
@@ -18482,16 +18482,16 @@
         <v>0</v>
       </c>
       <c r="U211">
-        <v>2.066115702479339</v>
+        <v>0.6578947368421052</v>
       </c>
       <c r="V211">
-        <v>3.305785123966942</v>
+        <v>2.631578947368421</v>
       </c>
       <c r="W211">
         <v>0</v>
       </c>
       <c r="X211">
-        <v>0.8264462809917356</v>
+        <v>0</v>
       </c>
       <c r="Y211">
         <v>0</v>
@@ -18502,28 +18502,28 @@
         <v>2024</v>
       </c>
       <c r="B212" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C212" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D212" t="s">
         <v>17</v>
       </c>
       <c r="E212">
-        <v>1.973684210526316</v>
+        <v>0</v>
       </c>
       <c r="F212">
         <v>0</v>
       </c>
       <c r="G212">
-        <v>0.6578947368421052</v>
+        <v>0</v>
       </c>
       <c r="H212">
         <v>0</v>
       </c>
       <c r="I212">
-        <v>2.631578947368421</v>
+        <v>4.6875</v>
       </c>
       <c r="J212">
         <v>0</v>
@@ -18532,13 +18532,13 @@
         <v>0</v>
       </c>
       <c r="L212">
-        <v>0</v>
+        <v>0.78125</v>
       </c>
       <c r="M212">
-        <v>2.631578947368421</v>
+        <v>0</v>
       </c>
       <c r="N212">
-        <v>5.263157894736842</v>
+        <v>0.78125</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -18550,7 +18550,7 @@
         <v>0</v>
       </c>
       <c r="R212">
-        <v>5.263157894736842</v>
+        <v>3.125</v>
       </c>
       <c r="S212">
         <v>0</v>
@@ -18559,16 +18559,16 @@
         <v>0</v>
       </c>
       <c r="U212">
-        <v>0.6578947368421052</v>
+        <v>0.78125</v>
       </c>
       <c r="V212">
-        <v>2.631578947368421</v>
+        <v>0</v>
       </c>
       <c r="W212">
         <v>0</v>
       </c>
       <c r="X212">
-        <v>0</v>
+        <v>2.34375</v>
       </c>
       <c r="Y212">
         <v>0</v>
@@ -18579,28 +18579,28 @@
         <v>2024</v>
       </c>
       <c r="B213" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C213" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D213" t="s">
         <v>17</v>
       </c>
       <c r="E213">
-        <v>0</v>
+        <v>1.15606936416185</v>
       </c>
       <c r="F213">
         <v>0</v>
       </c>
       <c r="G213">
-        <v>0</v>
+        <v>0.5780346820809248</v>
       </c>
       <c r="H213">
-        <v>0</v>
+        <v>0.5780346820809248</v>
       </c>
       <c r="I213">
-        <v>4.6875</v>
+        <v>0</v>
       </c>
       <c r="J213">
         <v>0</v>
@@ -18609,13 +18609,13 @@
         <v>0</v>
       </c>
       <c r="L213">
-        <v>0.78125</v>
+        <v>0</v>
       </c>
       <c r="M213">
         <v>0</v>
       </c>
       <c r="N213">
-        <v>0.78125</v>
+        <v>4.624277456647398</v>
       </c>
       <c r="O213">
         <v>0</v>
@@ -18627,7 +18627,7 @@
         <v>0</v>
       </c>
       <c r="R213">
-        <v>3.125</v>
+        <v>0</v>
       </c>
       <c r="S213">
         <v>0</v>
@@ -18636,16 +18636,16 @@
         <v>0</v>
       </c>
       <c r="U213">
-        <v>0.78125</v>
+        <v>1.15606936416185</v>
       </c>
       <c r="V213">
-        <v>0</v>
+        <v>0.5780346820809248</v>
       </c>
       <c r="W213">
-        <v>0</v>
+        <v>0.5780346820809248</v>
       </c>
       <c r="X213">
-        <v>2.34375</v>
+        <v>3.468208092485549</v>
       </c>
       <c r="Y213">
         <v>0</v>
@@ -18653,31 +18653,31 @@
     </row>
     <row r="214" spans="1:25">
       <c r="A214">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B214" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C214" t="s">
-        <v>415</v>
+        <v>305</v>
       </c>
       <c r="D214" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E214">
-        <v>1.15606936416185</v>
+        <v>1.680672268907563</v>
       </c>
       <c r="F214">
         <v>0</v>
       </c>
       <c r="G214">
-        <v>0.5780346820809248</v>
+        <v>0</v>
       </c>
       <c r="H214">
-        <v>0.5780346820809248</v>
+        <v>0</v>
       </c>
       <c r="I214">
-        <v>0</v>
+        <v>6.722689075630252</v>
       </c>
       <c r="J214">
         <v>0</v>
@@ -18692,7 +18692,7 @@
         <v>0</v>
       </c>
       <c r="N214">
-        <v>4.624277456647398</v>
+        <v>4.201680672268908</v>
       </c>
       <c r="O214">
         <v>0</v>
@@ -18701,7 +18701,7 @@
         <v>0</v>
       </c>
       <c r="Q214">
-        <v>0</v>
+        <v>2.521008403361344</v>
       </c>
       <c r="R214">
         <v>0</v>
@@ -18710,19 +18710,19 @@
         <v>0</v>
       </c>
       <c r="T214">
-        <v>0</v>
+        <v>0.8403361344537815</v>
       </c>
       <c r="U214">
-        <v>1.15606936416185</v>
+        <v>0</v>
       </c>
       <c r="V214">
-        <v>0.5780346820809248</v>
+        <v>0.8403361344537815</v>
       </c>
       <c r="W214">
-        <v>0.5780346820809248</v>
+        <v>2.521008403361344</v>
       </c>
       <c r="X214">
-        <v>3.468208092485549</v>
+        <v>0.8403361344537815</v>
       </c>
       <c r="Y214">
         <v>0</v>
@@ -18733,43 +18733,43 @@
         <v>2025</v>
       </c>
       <c r="B215" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C215" t="s">
-        <v>305</v>
+        <v>418</v>
       </c>
       <c r="D215" t="s">
         <v>11</v>
       </c>
       <c r="E215">
-        <v>1.680672268907563</v>
+        <v>1.530612244897959</v>
       </c>
       <c r="F215">
-        <v>0</v>
+        <v>7.142857142857142</v>
       </c>
       <c r="G215">
-        <v>0</v>
+        <v>2.040816326530612</v>
       </c>
       <c r="H215">
         <v>0</v>
       </c>
       <c r="I215">
-        <v>6.722689075630252</v>
+        <v>0</v>
       </c>
       <c r="J215">
-        <v>0</v>
+        <v>0.5102040816326531</v>
       </c>
       <c r="K215">
         <v>0</v>
       </c>
       <c r="L215">
-        <v>0</v>
+        <v>3.571428571428571</v>
       </c>
       <c r="M215">
         <v>0</v>
       </c>
       <c r="N215">
-        <v>4.201680672268908</v>
+        <v>0</v>
       </c>
       <c r="O215">
         <v>0</v>
@@ -18778,28 +18778,28 @@
         <v>0</v>
       </c>
       <c r="Q215">
-        <v>2.521008403361344</v>
+        <v>0</v>
       </c>
       <c r="R215">
-        <v>0</v>
+        <v>3.061224489795918</v>
       </c>
       <c r="S215">
         <v>0</v>
       </c>
       <c r="T215">
-        <v>0.8403361344537815</v>
+        <v>0</v>
       </c>
       <c r="U215">
         <v>0</v>
       </c>
       <c r="V215">
-        <v>0.8403361344537815</v>
+        <v>0.5102040816326531</v>
       </c>
       <c r="W215">
-        <v>2.521008403361344</v>
+        <v>0</v>
       </c>
       <c r="X215">
-        <v>0.8403361344537815</v>
+        <v>1.020408163265306</v>
       </c>
       <c r="Y215">
         <v>0</v>
@@ -18810,55 +18810,55 @@
         <v>2025</v>
       </c>
       <c r="B216" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C216" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D216" t="s">
         <v>11</v>
       </c>
       <c r="E216">
-        <v>1.530612244897959</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="F216">
-        <v>7.142857142857142</v>
+        <v>0</v>
       </c>
       <c r="G216">
-        <v>2.040816326530612</v>
+        <v>0</v>
       </c>
       <c r="H216">
-        <v>0</v>
+        <v>1.025641025641026</v>
       </c>
       <c r="I216">
-        <v>0</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="J216">
-        <v>0.5102040816326531</v>
+        <v>0</v>
       </c>
       <c r="K216">
         <v>0</v>
       </c>
       <c r="L216">
-        <v>3.571428571428571</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="M216">
-        <v>0</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="N216">
         <v>0</v>
       </c>
       <c r="O216">
-        <v>0</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="P216">
         <v>0</v>
       </c>
       <c r="Q216">
-        <v>0</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="R216">
-        <v>3.061224489795918</v>
+        <v>3.589743589743589</v>
       </c>
       <c r="S216">
         <v>0</v>
@@ -18867,19 +18867,19 @@
         <v>0</v>
       </c>
       <c r="U216">
-        <v>0</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="V216">
-        <v>0.5102040816326531</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="W216">
-        <v>0</v>
+        <v>1.025641025641026</v>
       </c>
       <c r="X216">
-        <v>1.020408163265306</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="Y216">
-        <v>0</v>
+        <v>0.5128205128205128</v>
       </c>
     </row>
     <row r="217" spans="1:25">
@@ -18887,76 +18887,76 @@
         <v>2025</v>
       </c>
       <c r="B217" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C217" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D217" t="s">
         <v>11</v>
       </c>
       <c r="E217">
-        <v>0.5128205128205128</v>
+        <v>0</v>
       </c>
       <c r="F217">
-        <v>0</v>
+        <v>0.3154574132492113</v>
       </c>
       <c r="G217">
-        <v>0</v>
+        <v>3.154574132492113</v>
       </c>
       <c r="H217">
-        <v>1.025641025641026</v>
+        <v>0</v>
       </c>
       <c r="I217">
-        <v>0.5128205128205128</v>
+        <v>0</v>
       </c>
       <c r="J217">
         <v>0</v>
       </c>
       <c r="K217">
-        <v>0</v>
+        <v>0.3154574132492113</v>
       </c>
       <c r="L217">
-        <v>0.5128205128205128</v>
+        <v>0.6309148264984227</v>
       </c>
       <c r="M217">
-        <v>0.5128205128205128</v>
+        <v>2.523659305993691</v>
       </c>
       <c r="N217">
-        <v>0</v>
+        <v>3.785488958990536</v>
       </c>
       <c r="O217">
-        <v>0.5128205128205128</v>
+        <v>0</v>
       </c>
       <c r="P217">
         <v>0</v>
       </c>
       <c r="Q217">
-        <v>0.5128205128205128</v>
+        <v>2.20820189274448</v>
       </c>
       <c r="R217">
-        <v>3.589743589743589</v>
+        <v>0.9463722397476341</v>
       </c>
       <c r="S217">
         <v>0</v>
       </c>
       <c r="T217">
-        <v>0</v>
+        <v>2.20820189274448</v>
       </c>
       <c r="U217">
-        <v>0.5128205128205128</v>
+        <v>0.3154574132492113</v>
       </c>
       <c r="V217">
-        <v>0.5128205128205128</v>
+        <v>1.577287066246057</v>
       </c>
       <c r="W217">
-        <v>1.025641025641026</v>
+        <v>0</v>
       </c>
       <c r="X217">
-        <v>0.5128205128205128</v>
+        <v>0.9463722397476341</v>
       </c>
       <c r="Y217">
-        <v>0.5128205128205128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:25">
@@ -18964,10 +18964,10 @@
         <v>2025</v>
       </c>
       <c r="B218" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C218" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D218" t="s">
         <v>11</v>
@@ -18976,10 +18976,10 @@
         <v>0</v>
       </c>
       <c r="F218">
-        <v>0.3154574132492113</v>
+        <v>0.4739336492890995</v>
       </c>
       <c r="G218">
-        <v>3.154574132492113</v>
+        <v>0</v>
       </c>
       <c r="H218">
         <v>0</v>
@@ -18991,46 +18991,46 @@
         <v>0</v>
       </c>
       <c r="K218">
-        <v>0.3154574132492113</v>
+        <v>0</v>
       </c>
       <c r="L218">
-        <v>0.6309148264984227</v>
+        <v>1.421800947867299</v>
       </c>
       <c r="M218">
-        <v>2.523659305993691</v>
+        <v>0.4739336492890995</v>
       </c>
       <c r="N218">
-        <v>3.785488958990536</v>
+        <v>1.421800947867299</v>
       </c>
       <c r="O218">
-        <v>0</v>
+        <v>0.4739336492890995</v>
       </c>
       <c r="P218">
         <v>0</v>
       </c>
       <c r="Q218">
-        <v>2.20820189274448</v>
+        <v>0.9478672985781991</v>
       </c>
       <c r="R218">
-        <v>0.9463722397476341</v>
+        <v>0</v>
       </c>
       <c r="S218">
         <v>0</v>
       </c>
       <c r="T218">
-        <v>2.20820189274448</v>
+        <v>1.421800947867299</v>
       </c>
       <c r="U218">
-        <v>0.3154574132492113</v>
+        <v>1.421800947867299</v>
       </c>
       <c r="V218">
-        <v>1.577287066246057</v>
+        <v>1.421800947867299</v>
       </c>
       <c r="W218">
         <v>0</v>
       </c>
       <c r="X218">
-        <v>0.9463722397476341</v>
+        <v>1.421800947867299</v>
       </c>
       <c r="Y218">
         <v>0</v>
@@ -19041,10 +19041,10 @@
         <v>2025</v>
       </c>
       <c r="B219" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C219" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D219" t="s">
         <v>11</v>
@@ -19053,10 +19053,10 @@
         <v>0</v>
       </c>
       <c r="F219">
-        <v>0.4739336492890995</v>
+        <v>0.2994011976047904</v>
       </c>
       <c r="G219">
-        <v>0</v>
+        <v>1.497005988023952</v>
       </c>
       <c r="H219">
         <v>0</v>
@@ -19065,49 +19065,49 @@
         <v>0</v>
       </c>
       <c r="J219">
-        <v>0</v>
+        <v>2.095808383233533</v>
       </c>
       <c r="K219">
         <v>0</v>
       </c>
       <c r="L219">
-        <v>1.421800947867299</v>
+        <v>0.5988023952095809</v>
       </c>
       <c r="M219">
-        <v>0.4739336492890995</v>
+        <v>0.5988023952095809</v>
       </c>
       <c r="N219">
-        <v>1.421800947867299</v>
+        <v>4.491017964071856</v>
       </c>
       <c r="O219">
-        <v>0.4739336492890995</v>
+        <v>0</v>
       </c>
       <c r="P219">
-        <v>0</v>
+        <v>0.5988023952095809</v>
       </c>
       <c r="Q219">
-        <v>0.9478672985781991</v>
+        <v>1.197604790419162</v>
       </c>
       <c r="R219">
-        <v>0</v>
+        <v>0.2994011976047904</v>
       </c>
       <c r="S219">
-        <v>0</v>
+        <v>0.5988023952095809</v>
       </c>
       <c r="T219">
-        <v>1.421800947867299</v>
+        <v>0.2994011976047904</v>
       </c>
       <c r="U219">
-        <v>1.421800947867299</v>
+        <v>0.2994011976047904</v>
       </c>
       <c r="V219">
-        <v>1.421800947867299</v>
+        <v>5.688622754491018</v>
       </c>
       <c r="W219">
         <v>0</v>
       </c>
       <c r="X219">
-        <v>1.421800947867299</v>
+        <v>3.892215568862276</v>
       </c>
       <c r="Y219">
         <v>0</v>
@@ -19118,10 +19118,10 @@
         <v>2025</v>
       </c>
       <c r="B220" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C220" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D220" t="s">
         <v>11</v>
@@ -19130,61 +19130,61 @@
         <v>0</v>
       </c>
       <c r="F220">
-        <v>0.2994011976047904</v>
+        <v>2.8328611898017</v>
       </c>
       <c r="G220">
-        <v>1.497005988023952</v>
+        <v>4.53257790368272</v>
       </c>
       <c r="H220">
         <v>0</v>
       </c>
       <c r="I220">
-        <v>0</v>
+        <v>0.28328611898017</v>
       </c>
       <c r="J220">
-        <v>2.095808383233533</v>
+        <v>0.84985835694051</v>
       </c>
       <c r="K220">
         <v>0</v>
       </c>
       <c r="L220">
-        <v>0.5988023952095809</v>
+        <v>0.56657223796034</v>
       </c>
       <c r="M220">
-        <v>0.5988023952095809</v>
+        <v>0.84985835694051</v>
       </c>
       <c r="N220">
-        <v>4.491017964071856</v>
+        <v>1.13314447592068</v>
       </c>
       <c r="O220">
-        <v>0</v>
+        <v>0.28328611898017</v>
       </c>
       <c r="P220">
-        <v>0.5988023952095809</v>
+        <v>0</v>
       </c>
       <c r="Q220">
-        <v>1.197604790419162</v>
+        <v>0</v>
       </c>
       <c r="R220">
-        <v>0.2994011976047904</v>
+        <v>4.815864022662889</v>
       </c>
       <c r="S220">
-        <v>0.5988023952095809</v>
+        <v>0</v>
       </c>
       <c r="T220">
-        <v>0.2994011976047904</v>
+        <v>0</v>
       </c>
       <c r="U220">
-        <v>0.2994011976047904</v>
+        <v>0</v>
       </c>
       <c r="V220">
-        <v>5.688622754491018</v>
+        <v>2.26628895184136</v>
       </c>
       <c r="W220">
-        <v>0</v>
+        <v>1.13314447592068</v>
       </c>
       <c r="X220">
-        <v>3.892215568862276</v>
+        <v>0.56657223796034</v>
       </c>
       <c r="Y220">
         <v>0</v>
@@ -19195,10 +19195,10 @@
         <v>2025</v>
       </c>
       <c r="B221" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C221" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D221" t="s">
         <v>11</v>
@@ -19207,43 +19207,43 @@
         <v>0</v>
       </c>
       <c r="F221">
-        <v>2.8328611898017</v>
+        <v>0</v>
       </c>
       <c r="G221">
-        <v>4.53257790368272</v>
+        <v>0.5025125628140703</v>
       </c>
       <c r="H221">
         <v>0</v>
       </c>
       <c r="I221">
-        <v>0.28328611898017</v>
+        <v>0</v>
       </c>
       <c r="J221">
-        <v>0.84985835694051</v>
+        <v>0</v>
       </c>
       <c r="K221">
         <v>0</v>
       </c>
       <c r="L221">
-        <v>0.56657223796034</v>
+        <v>0</v>
       </c>
       <c r="M221">
-        <v>0.84985835694051</v>
+        <v>0.5025125628140703</v>
       </c>
       <c r="N221">
-        <v>1.13314447592068</v>
+        <v>2.512562814070352</v>
       </c>
       <c r="O221">
-        <v>0.28328611898017</v>
+        <v>1.005025125628141</v>
       </c>
       <c r="P221">
-        <v>0</v>
+        <v>0.5025125628140703</v>
       </c>
       <c r="Q221">
         <v>0</v>
       </c>
       <c r="R221">
-        <v>4.815864022662889</v>
+        <v>0</v>
       </c>
       <c r="S221">
         <v>0</v>
@@ -19255,16 +19255,16 @@
         <v>0</v>
       </c>
       <c r="V221">
-        <v>2.26628895184136</v>
+        <v>1.507537688442211</v>
       </c>
       <c r="W221">
-        <v>1.13314447592068</v>
+        <v>0.5025125628140703</v>
       </c>
       <c r="X221">
-        <v>0.56657223796034</v>
+        <v>1.005025125628141</v>
       </c>
       <c r="Y221">
-        <v>0</v>
+        <v>0.5025125628140703</v>
       </c>
     </row>
     <row r="222" spans="1:25">
@@ -19272,22 +19272,22 @@
         <v>2025</v>
       </c>
       <c r="B222" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C222" t="s">
-        <v>430</v>
+        <v>159</v>
       </c>
       <c r="D222" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E222">
         <v>0</v>
       </c>
       <c r="F222">
-        <v>0</v>
+        <v>3.703703703703703</v>
       </c>
       <c r="G222">
-        <v>0.5025125628140703</v>
+        <v>3.08641975308642</v>
       </c>
       <c r="H222">
         <v>0</v>
@@ -19305,22 +19305,22 @@
         <v>0</v>
       </c>
       <c r="M222">
-        <v>0.5025125628140703</v>
+        <v>0</v>
       </c>
       <c r="N222">
-        <v>2.512562814070352</v>
+        <v>3.703703703703703</v>
       </c>
       <c r="O222">
-        <v>1.005025125628141</v>
+        <v>0</v>
       </c>
       <c r="P222">
-        <v>0.5025125628140703</v>
+        <v>0</v>
       </c>
       <c r="Q222">
-        <v>0</v>
+        <v>1.234567901234568</v>
       </c>
       <c r="R222">
-        <v>0</v>
+        <v>1.234567901234568</v>
       </c>
       <c r="S222">
         <v>0</v>
@@ -19329,19 +19329,19 @@
         <v>0</v>
       </c>
       <c r="U222">
-        <v>0</v>
+        <v>0.6172839506172839</v>
       </c>
       <c r="V222">
-        <v>1.507537688442211</v>
+        <v>6.172839506172839</v>
       </c>
       <c r="W222">
-        <v>0.5025125628140703</v>
+        <v>0.6172839506172839</v>
       </c>
       <c r="X222">
-        <v>1.005025125628141</v>
+        <v>0.6172839506172839</v>
       </c>
       <c r="Y222">
-        <v>0.5025125628140703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:25">
@@ -19349,10 +19349,10 @@
         <v>2025</v>
       </c>
       <c r="B223" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C223" t="s">
-        <v>159</v>
+        <v>408</v>
       </c>
       <c r="D223" t="s">
         <v>17</v>
@@ -19361,13 +19361,13 @@
         <v>0</v>
       </c>
       <c r="F223">
-        <v>3.703703703703703</v>
+        <v>0</v>
       </c>
       <c r="G223">
-        <v>3.08641975308642</v>
+        <v>0</v>
       </c>
       <c r="H223">
-        <v>0</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="I223">
         <v>0</v>
@@ -19385,40 +19385,40 @@
         <v>0</v>
       </c>
       <c r="N223">
-        <v>3.703703703703703</v>
+        <v>6.363636363636363</v>
       </c>
       <c r="O223">
         <v>0</v>
       </c>
       <c r="P223">
-        <v>0</v>
+        <v>4.545454545454546</v>
       </c>
       <c r="Q223">
-        <v>1.234567901234568</v>
+        <v>0</v>
       </c>
       <c r="R223">
-        <v>1.234567901234568</v>
+        <v>1.818181818181818</v>
       </c>
       <c r="S223">
-        <v>0</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="T223">
-        <v>0</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="U223">
-        <v>0.6172839506172839</v>
+        <v>0</v>
       </c>
       <c r="V223">
-        <v>6.172839506172839</v>
+        <v>2.727272727272727</v>
       </c>
       <c r="W223">
-        <v>0.6172839506172839</v>
+        <v>0</v>
       </c>
       <c r="X223">
-        <v>0.6172839506172839</v>
+        <v>1.818181818181818</v>
       </c>
       <c r="Y223">
-        <v>0</v>
+        <v>0.9090909090909091</v>
       </c>
     </row>
     <row r="224" spans="1:25">
@@ -19426,10 +19426,10 @@
         <v>2025</v>
       </c>
       <c r="B224" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C224" t="s">
-        <v>408</v>
+        <v>95</v>
       </c>
       <c r="D224" t="s">
         <v>17</v>
@@ -19444,58 +19444,58 @@
         <v>0</v>
       </c>
       <c r="H224">
-        <v>0.9090909090909091</v>
+        <v>0</v>
       </c>
       <c r="I224">
-        <v>0</v>
+        <v>1.449275362318841</v>
       </c>
       <c r="J224">
-        <v>0</v>
+        <v>0.7246376811594203</v>
       </c>
       <c r="K224">
-        <v>0</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="L224">
-        <v>0</v>
+        <v>0.7246376811594203</v>
       </c>
       <c r="M224">
         <v>0</v>
       </c>
       <c r="N224">
-        <v>6.363636363636363</v>
+        <v>2.898550724637681</v>
       </c>
       <c r="O224">
         <v>0</v>
       </c>
       <c r="P224">
-        <v>4.545454545454546</v>
+        <v>0.7246376811594203</v>
       </c>
       <c r="Q224">
         <v>0</v>
       </c>
       <c r="R224">
-        <v>1.818181818181818</v>
+        <v>0</v>
       </c>
       <c r="S224">
-        <v>0.9090909090909091</v>
+        <v>0</v>
       </c>
       <c r="T224">
-        <v>0.9090909090909091</v>
+        <v>0</v>
       </c>
       <c r="U224">
-        <v>0</v>
+        <v>1.449275362318841</v>
       </c>
       <c r="V224">
-        <v>2.727272727272727</v>
+        <v>1.449275362318841</v>
       </c>
       <c r="W224">
-        <v>0</v>
+        <v>0.7246376811594203</v>
       </c>
       <c r="X224">
-        <v>1.818181818181818</v>
+        <v>2.173913043478261</v>
       </c>
       <c r="Y224">
-        <v>0.9090909090909091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225" spans="1:25">
@@ -19503,10 +19503,10 @@
         <v>2025</v>
       </c>
       <c r="B225" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C225" t="s">
-        <v>95</v>
+        <v>365</v>
       </c>
       <c r="D225" t="s">
         <v>17</v>
@@ -19518,37 +19518,37 @@
         <v>0</v>
       </c>
       <c r="G225">
-        <v>0</v>
+        <v>2.325581395348837</v>
       </c>
       <c r="H225">
         <v>0</v>
       </c>
       <c r="I225">
-        <v>1.449275362318841</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="J225">
-        <v>0.7246376811594203</v>
+        <v>0</v>
       </c>
       <c r="K225">
-        <v>4.347826086956522</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="L225">
-        <v>0.7246376811594203</v>
+        <v>0</v>
       </c>
       <c r="M225">
         <v>0</v>
       </c>
       <c r="N225">
-        <v>2.898550724637681</v>
+        <v>4.651162790697675</v>
       </c>
       <c r="O225">
         <v>0</v>
       </c>
       <c r="P225">
-        <v>0.7246376811594203</v>
+        <v>0</v>
       </c>
       <c r="Q225">
-        <v>0</v>
+        <v>1.395348837209302</v>
       </c>
       <c r="R225">
         <v>0</v>
@@ -19560,16 +19560,16 @@
         <v>0</v>
       </c>
       <c r="U225">
-        <v>1.449275362318841</v>
+        <v>0.9302325581395349</v>
       </c>
       <c r="V225">
-        <v>1.449275362318841</v>
+        <v>1.86046511627907</v>
       </c>
       <c r="W225">
-        <v>0.7246376811594203</v>
+        <v>0.9302325581395349</v>
       </c>
       <c r="X225">
-        <v>2.173913043478261</v>
+        <v>0</v>
       </c>
       <c r="Y225">
         <v>0</v>
@@ -19580,7 +19580,7 @@
         <v>2025</v>
       </c>
       <c r="B226" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C226" t="s">
         <v>365</v>
@@ -19592,40 +19592,40 @@
         <v>0</v>
       </c>
       <c r="F226">
-        <v>0</v>
+        <v>2.515723270440252</v>
       </c>
       <c r="G226">
-        <v>2.325581395348837</v>
+        <v>0</v>
       </c>
       <c r="H226">
-        <v>0</v>
+        <v>5.660377358490567</v>
       </c>
       <c r="I226">
-        <v>0.4651162790697674</v>
+        <v>0</v>
       </c>
       <c r="J226">
         <v>0</v>
       </c>
       <c r="K226">
-        <v>0.4651162790697674</v>
+        <v>0</v>
       </c>
       <c r="L226">
         <v>0</v>
       </c>
       <c r="M226">
-        <v>0</v>
+        <v>0.628930817610063</v>
       </c>
       <c r="N226">
-        <v>4.651162790697675</v>
+        <v>10.69182389937107</v>
       </c>
       <c r="O226">
         <v>0</v>
       </c>
       <c r="P226">
-        <v>0</v>
+        <v>1.257861635220126</v>
       </c>
       <c r="Q226">
-        <v>1.395348837209302</v>
+        <v>0</v>
       </c>
       <c r="R226">
         <v>0</v>
@@ -19637,95 +19637,18 @@
         <v>0</v>
       </c>
       <c r="U226">
-        <v>0.9302325581395349</v>
+        <v>0</v>
       </c>
       <c r="V226">
-        <v>1.86046511627907</v>
+        <v>3.144654088050315</v>
       </c>
       <c r="W226">
-        <v>0.9302325581395349</v>
+        <v>0</v>
       </c>
       <c r="X226">
         <v>0</v>
       </c>
       <c r="Y226">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="1:25">
-      <c r="A227">
-        <v>2025</v>
-      </c>
-      <c r="B227" t="s">
-        <v>435</v>
-      </c>
-      <c r="C227" t="s">
-        <v>365</v>
-      </c>
-      <c r="D227" t="s">
-        <v>17</v>
-      </c>
-      <c r="E227">
-        <v>0</v>
-      </c>
-      <c r="F227">
-        <v>2.515723270440252</v>
-      </c>
-      <c r="G227">
-        <v>0</v>
-      </c>
-      <c r="H227">
-        <v>5.660377358490567</v>
-      </c>
-      <c r="I227">
-        <v>0</v>
-      </c>
-      <c r="J227">
-        <v>0</v>
-      </c>
-      <c r="K227">
-        <v>0</v>
-      </c>
-      <c r="L227">
-        <v>0</v>
-      </c>
-      <c r="M227">
-        <v>0.628930817610063</v>
-      </c>
-      <c r="N227">
-        <v>10.69182389937107</v>
-      </c>
-      <c r="O227">
-        <v>0</v>
-      </c>
-      <c r="P227">
-        <v>1.257861635220126</v>
-      </c>
-      <c r="Q227">
-        <v>0</v>
-      </c>
-      <c r="R227">
-        <v>0</v>
-      </c>
-      <c r="S227">
-        <v>0</v>
-      </c>
-      <c r="T227">
-        <v>0</v>
-      </c>
-      <c r="U227">
-        <v>0</v>
-      </c>
-      <c r="V227">
-        <v>3.144654088050315</v>
-      </c>
-      <c r="W227">
-        <v>0</v>
-      </c>
-      <c r="X227">
-        <v>0</v>
-      </c>
-      <c r="Y227">
         <v>0</v>
       </c>
     </row>

--- a/resultados/analisis_genero_tematico.xlsx
+++ b/resultados/analisis_genero_tematico.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="449">
   <si>
     <t>categoria</t>
   </si>
@@ -41,6 +41,15 @@
     <t>mayor_en</t>
   </si>
   <si>
+    <t>p_ajustado</t>
+  </si>
+  <si>
+    <t>p_ajustado_fmt</t>
+  </si>
+  <si>
+    <t>significativa_bh</t>
+  </si>
+  <si>
     <t>CALLE_IDENTIDAD</t>
   </si>
   <si>
@@ -56,12 +65,21 @@
     <t>ONOMATOPEYAS</t>
   </si>
   <si>
+    <t>0.006</t>
+  </si>
+  <si>
     <t>MOVILIDAD</t>
   </si>
   <si>
     <t>0.01</t>
   </si>
   <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>MUSICA_CULTURA</t>
   </si>
   <si>
@@ -71,6 +89,9 @@
     <t>Mujer</t>
   </si>
   <si>
+    <t>0.185</t>
+  </si>
+  <si>
     <t>DROGAS</t>
   </si>
   <si>
@@ -83,7 +104,7 @@
     <t>0.061</t>
   </si>
   <si>
-    <t>No</t>
+    <t>0.213</t>
   </si>
   <si>
     <t>RELIGION_IMAGINARIOS</t>
@@ -92,6 +113,9 @@
     <t>0.195</t>
   </si>
   <si>
+    <t>0.48</t>
+  </si>
+  <si>
     <t>DISCRIMINACION</t>
   </si>
   <si>
@@ -119,6 +143,9 @@
     <t>0.307</t>
   </si>
   <si>
+    <t>0.534</t>
+  </si>
+  <si>
     <t>SEXUALIDAD</t>
   </si>
   <si>
@@ -137,30 +164,45 @@
     <t>0.43</t>
   </si>
   <si>
+    <t>0.602</t>
+  </si>
+  <si>
     <t>GENERO_PODER</t>
   </si>
   <si>
     <t>0.527</t>
   </si>
   <si>
+    <t>0.692</t>
+  </si>
+  <si>
     <t>NOCTURNIDAD</t>
   </si>
   <si>
     <t>0.728</t>
   </si>
   <si>
+    <t>0.9</t>
+  </si>
+  <si>
     <t>EMOCIONES</t>
   </si>
   <si>
     <t>0.826</t>
   </si>
   <si>
+    <t>0.964</t>
+  </si>
+  <si>
     <t>PRESTIGIO_CONFLICTO</t>
   </si>
   <si>
     <t>0.982</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>ROMANCE</t>
   </si>
   <si>
@@ -168,9 +210,6 @@
   </si>
   <si>
     <t>VIOLENCIA</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>año</t>
@@ -1668,10 +1707,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1">
+    <row r="1" spans="1:11" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1696,10 +1735,19 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>2.0997</v>
@@ -1711,21 +1759,30 @@
         <v>1.1875</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F2">
         <v>0.312</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>14</v>
+      </c>
+      <c r="I2">
+        <v>5.823893908596389E-05</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>2.3623</v>
@@ -1737,21 +1794,30 @@
         <v>0.7904</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3">
         <v>0.229</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>14</v>
+      </c>
+      <c r="I3">
+        <v>0.006375773005178997</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4">
         <v>0.3642</v>
@@ -1763,21 +1829,30 @@
         <v>0.1706</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F4">
         <v>0.172</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>14</v>
+      </c>
+      <c r="I4">
+        <v>0.06859740437064987</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>0.3693</v>
@@ -1789,21 +1864,30 @@
         <v>-0.1024</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>0.138</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>23</v>
+      </c>
+      <c r="I5">
+        <v>0.184781012627073</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>0.4179</v>
@@ -1815,21 +1899,30 @@
         <v>0.209</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F6">
         <v>0.134</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>0.184781012627073</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B7">
         <v>0.4416</v>
@@ -1841,21 +1934,30 @@
         <v>0.0533</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F7">
         <v>0.125</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>14</v>
+      </c>
+      <c r="I7">
+        <v>0.2129340027669805</v>
+      </c>
+      <c r="J7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B8">
         <v>0.3783</v>
@@ -1867,21 +1969,30 @@
         <v>-0.2536</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F8">
         <v>0.08599999999999999</v>
       </c>
       <c r="G8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>23</v>
+      </c>
+      <c r="I8">
+        <v>0.4803898295699837</v>
+      </c>
+      <c r="J8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B9">
         <v>0.1512</v>
@@ -1893,21 +2004,30 @@
         <v>-0.1034</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F9">
         <v>0.082</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>23</v>
+      </c>
+      <c r="I9">
+        <v>0.4803898295699837</v>
+      </c>
+      <c r="J9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B10">
         <v>0.256</v>
@@ -1919,21 +2039,30 @@
         <v>0.055</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F10">
         <v>0.082</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>14</v>
+      </c>
+      <c r="I10">
+        <v>0.4803898295699837</v>
+      </c>
+      <c r="J10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B11">
         <v>0.2157</v>
@@ -1945,21 +2074,30 @@
         <v>-0.2808</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F11">
         <v>0.08</v>
       </c>
       <c r="G11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>23</v>
+      </c>
+      <c r="I11">
+        <v>0.4803898295699837</v>
+      </c>
+      <c r="J11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B12">
         <v>1.3235</v>
@@ -1971,21 +2109,30 @@
         <v>0.1878</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F12">
         <v>0.076</v>
       </c>
       <c r="G12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>14</v>
+      </c>
+      <c r="I12">
+        <v>0.4803898295699837</v>
+      </c>
+      <c r="J12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B13">
         <v>0.4015</v>
@@ -1997,21 +2144,30 @@
         <v>0.1456</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F13">
         <v>0.068</v>
       </c>
       <c r="G13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>14</v>
+      </c>
+      <c r="I13">
+        <v>0.5342871815336163</v>
+      </c>
+      <c r="J13" t="s">
+        <v>42</v>
+      </c>
+      <c r="K13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B14">
         <v>1.0252</v>
@@ -2023,21 +2179,30 @@
         <v>-0.0911</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F14">
         <v>0.064</v>
       </c>
       <c r="G14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>23</v>
+      </c>
+      <c r="I14">
+        <v>0.5342871815336163</v>
+      </c>
+      <c r="J14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B15">
         <v>0.9095</v>
@@ -2049,21 +2214,30 @@
         <v>-0.0673</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F15">
         <v>0.062</v>
       </c>
       <c r="G15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>23</v>
+      </c>
+      <c r="I15">
+        <v>0.5342871815336163</v>
+      </c>
+      <c r="J15" t="s">
+        <v>42</v>
+      </c>
+      <c r="K15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B16">
         <v>1.6383</v>
@@ -2075,21 +2249,30 @@
         <v>-0.1261</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F16">
         <v>0.053</v>
       </c>
       <c r="G16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>23</v>
+      </c>
+      <c r="I16">
+        <v>0.6023034823044506</v>
+      </c>
+      <c r="J16" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>2.9652</v>
@@ -2101,21 +2284,30 @@
         <v>-0.1105</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F17">
         <v>0.042</v>
       </c>
       <c r="G17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>23</v>
+      </c>
+      <c r="I17">
+        <v>0.6916903843674771</v>
+      </c>
+      <c r="J17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B18">
         <v>0.5253</v>
@@ -2127,21 +2319,30 @@
         <v>0.0228</v>
       </c>
       <c r="E18" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F18">
         <v>0.023</v>
       </c>
       <c r="G18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>14</v>
+      </c>
+      <c r="I18">
+        <v>0.8997934900564464</v>
+      </c>
+      <c r="J18" t="s">
+        <v>55</v>
+      </c>
+      <c r="K18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B19">
         <v>0.6486</v>
@@ -2153,21 +2354,30 @@
         <v>-0.1492</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F19">
         <v>0.015</v>
       </c>
       <c r="G19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>23</v>
+      </c>
+      <c r="I19">
+        <v>0.9641950684397904</v>
+      </c>
+      <c r="J19" t="s">
+        <v>58</v>
+      </c>
+      <c r="K19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B20">
         <v>0.214</v>
@@ -2179,21 +2389,30 @@
         <v>-0.0249</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F20">
         <v>0.002</v>
       </c>
       <c r="G20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>23</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20" t="s">
+        <v>61</v>
+      </c>
+      <c r="K20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="B21">
         <v>1.3241</v>
@@ -2205,21 +2424,30 @@
         <v>-0.3805</v>
       </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F21">
         <v>0.001</v>
       </c>
       <c r="G21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+        <v>23</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21" t="s">
+        <v>61</v>
+      </c>
+      <c r="K21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B22">
         <v>0.1776</v>
@@ -2231,16 +2459,25 @@
         <v>-0.0106</v>
       </c>
       <c r="E22" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H22" t="s">
-        <v>17</v>
+        <v>23</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22" t="s">
+        <v>61</v>
+      </c>
+      <c r="K22" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2255,79 +2492,79 @@
   <sheetData>
     <row r="1" spans="1:25" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:25">
@@ -2335,13 +2572,13 @@
         <v>2010</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -2412,13 +2649,13 @@
         <v>2010</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -2489,13 +2726,13 @@
         <v>2010</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -2566,13 +2803,13 @@
         <v>2010</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2643,13 +2880,13 @@
         <v>2010</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -2720,13 +2957,13 @@
         <v>2010</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>0.6134969325153374</v>
@@ -2797,13 +3034,13 @@
         <v>2010</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -2874,13 +3111,13 @@
         <v>2010</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -2951,13 +3188,13 @@
         <v>2010</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -3028,13 +3265,13 @@
         <v>2010</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -3105,13 +3342,13 @@
         <v>2010</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -3182,13 +3419,13 @@
         <v>2010</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -3259,13 +3496,13 @@
         <v>2010</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -3336,13 +3573,13 @@
         <v>2010</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -3413,13 +3650,13 @@
         <v>2010</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -3490,13 +3727,13 @@
         <v>2011</v>
       </c>
       <c r="B17" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -3567,13 +3804,13 @@
         <v>2011</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -3644,13 +3881,13 @@
         <v>2011</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -3721,13 +3958,13 @@
         <v>2011</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="D20" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -3798,13 +4035,13 @@
         <v>2011</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -3875,13 +4112,13 @@
         <v>2011</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -3952,13 +4189,13 @@
         <v>2011</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E23">
         <v>0.6153846153846154</v>
@@ -4029,13 +4266,13 @@
         <v>2011</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4106,13 +4343,13 @@
         <v>2011</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D25" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4183,13 +4420,13 @@
         <v>2011</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D26" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4260,13 +4497,13 @@
         <v>2011</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -4337,13 +4574,13 @@
         <v>2011</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4414,13 +4651,13 @@
         <v>2011</v>
       </c>
       <c r="B29" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C29" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4491,13 +4728,13 @@
         <v>2011</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4568,13 +4805,13 @@
         <v>2011</v>
       </c>
       <c r="B31" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -4645,13 +4882,13 @@
         <v>2012</v>
       </c>
       <c r="B32" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="C32" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -4722,13 +4959,13 @@
         <v>2012</v>
       </c>
       <c r="B33" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="C33" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -4799,13 +5036,13 @@
         <v>2012</v>
       </c>
       <c r="B34" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D34" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -4876,13 +5113,13 @@
         <v>2012</v>
       </c>
       <c r="B35" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="C35" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D35" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -4953,13 +5190,13 @@
         <v>2012</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="C36" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="D36" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -5030,13 +5267,13 @@
         <v>2012</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="C37" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="D37" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E37">
         <v>1.255230125523012</v>
@@ -5107,13 +5344,13 @@
         <v>2012</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D38" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -5184,13 +5421,13 @@
         <v>2012</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="C39" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="D39" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E39">
         <v>1.08695652173913</v>
@@ -5261,13 +5498,13 @@
         <v>2012</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="D40" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E40">
         <v>0.4</v>
@@ -5338,13 +5575,13 @@
         <v>2012</v>
       </c>
       <c r="B41" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="C41" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D41" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5415,13 +5652,13 @@
         <v>2012</v>
       </c>
       <c r="B42" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C42" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D42" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -5492,13 +5729,13 @@
         <v>2012</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="C43" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D43" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -5569,13 +5806,13 @@
         <v>2012</v>
       </c>
       <c r="B44" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C44" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D44" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -5646,13 +5883,13 @@
         <v>2012</v>
       </c>
       <c r="B45" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="C45" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D45" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -5723,13 +5960,13 @@
         <v>2013</v>
       </c>
       <c r="B46" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="C46" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D46" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -5800,13 +6037,13 @@
         <v>2013</v>
       </c>
       <c r="B47" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="D47" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -5877,13 +6114,13 @@
         <v>2013</v>
       </c>
       <c r="B48" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="C48" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="D48" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -5954,13 +6191,13 @@
         <v>2013</v>
       </c>
       <c r="B49" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C49" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="D49" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -6031,13 +6268,13 @@
         <v>2013</v>
       </c>
       <c r="B50" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="C50" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="D50" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -6108,13 +6345,13 @@
         <v>2013</v>
       </c>
       <c r="B51" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="C51" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D51" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -6185,13 +6422,13 @@
         <v>2013</v>
       </c>
       <c r="B52" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="C52" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="D52" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -6262,13 +6499,13 @@
         <v>2013</v>
       </c>
       <c r="B53" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="C53" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D53" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E53">
         <v>0.7575757575757576</v>
@@ -6339,13 +6576,13 @@
         <v>2013</v>
       </c>
       <c r="B54" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="C54" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D54" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E54">
         <v>0.5602240896358543</v>
@@ -6416,13 +6653,13 @@
         <v>2013</v>
       </c>
       <c r="B55" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C55" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="D55" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E55">
         <v>0.3048780487804878</v>
@@ -6493,13 +6730,13 @@
         <v>2013</v>
       </c>
       <c r="B56" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C56" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D56" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -6570,13 +6807,13 @@
         <v>2013</v>
       </c>
       <c r="B57" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C57" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D57" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -6647,13 +6884,13 @@
         <v>2013</v>
       </c>
       <c r="B58" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="C58" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="D58" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -6724,10 +6961,10 @@
         <v>2013</v>
       </c>
       <c r="C59" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="D59" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E59">
         <v>1.25</v>
@@ -6798,13 +7035,13 @@
         <v>2013</v>
       </c>
       <c r="B60" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C60" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D60" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -6875,13 +7112,13 @@
         <v>2014</v>
       </c>
       <c r="B61" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="C61" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="D61" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -6952,13 +7189,13 @@
         <v>2014</v>
       </c>
       <c r="B62" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C62" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D62" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E62">
         <v>0.3164556962025317</v>
@@ -7029,13 +7266,13 @@
         <v>2014</v>
       </c>
       <c r="B63" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="C63" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="D63" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E63">
         <v>1.415094339622642</v>
@@ -7106,13 +7343,13 @@
         <v>2014</v>
       </c>
       <c r="B64" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="C64" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="D64" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -7183,13 +7420,13 @@
         <v>2014</v>
       </c>
       <c r="B65" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="C65" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="D65" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E65">
         <v>1.183431952662722</v>
@@ -7260,13 +7497,13 @@
         <v>2014</v>
       </c>
       <c r="B66" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="C66" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="D66" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -7337,13 +7574,13 @@
         <v>2014</v>
       </c>
       <c r="B67" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="C67" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="D67" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -7414,13 +7651,13 @@
         <v>2014</v>
       </c>
       <c r="B68" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C68" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D68" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E68">
         <v>0.3194888178913738</v>
@@ -7491,13 +7728,13 @@
         <v>2014</v>
       </c>
       <c r="B69" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="C69" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -7568,13 +7805,13 @@
         <v>2014</v>
       </c>
       <c r="B70" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C70" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="D70" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -7645,13 +7882,13 @@
         <v>2014</v>
       </c>
       <c r="B71" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="C71" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D71" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -7722,13 +7959,13 @@
         <v>2014</v>
       </c>
       <c r="B72" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="C72" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D72" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -7799,13 +8036,13 @@
         <v>2014</v>
       </c>
       <c r="B73" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C73" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D73" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -7876,13 +8113,13 @@
         <v>2014</v>
       </c>
       <c r="B74" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="C74" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="D74" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -7953,13 +8190,13 @@
         <v>2014</v>
       </c>
       <c r="B75" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="C75" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D75" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -8030,13 +8267,13 @@
         <v>2015</v>
       </c>
       <c r="B76" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="C76" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="D76" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -8107,13 +8344,13 @@
         <v>2015</v>
       </c>
       <c r="B77" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="C77" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D77" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E77">
         <v>2.05761316872428</v>
@@ -8184,13 +8421,13 @@
         <v>2015</v>
       </c>
       <c r="B78" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="C78" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="D78" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -8261,13 +8498,13 @@
         <v>2015</v>
       </c>
       <c r="B79" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="C79" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D79" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -8338,13 +8575,13 @@
         <v>2015</v>
       </c>
       <c r="B80" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="C80" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D80" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E80">
         <v>0.4464285714285714</v>
@@ -8415,13 +8652,13 @@
         <v>2015</v>
       </c>
       <c r="B81" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="C81" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="D81" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -8492,13 +8729,13 @@
         <v>2015</v>
       </c>
       <c r="B82" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="C82" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="D82" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E82">
         <v>0.8547008547008548</v>
@@ -8569,13 +8806,13 @@
         <v>2015</v>
       </c>
       <c r="B83" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="C83" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D83" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -8646,13 +8883,13 @@
         <v>2015</v>
       </c>
       <c r="B84" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="C84" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="D84" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -8723,13 +8960,13 @@
         <v>2015</v>
       </c>
       <c r="B85" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="C85" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="D85" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -8800,13 +9037,13 @@
         <v>2015</v>
       </c>
       <c r="B86" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="C86" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D86" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -8877,13 +9114,13 @@
         <v>2015</v>
       </c>
       <c r="B87" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C87" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D87" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -8954,13 +9191,13 @@
         <v>2015</v>
       </c>
       <c r="B88" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="C88" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D88" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -9031,13 +9268,13 @@
         <v>2015</v>
       </c>
       <c r="B89" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="C89" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D89" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -9108,13 +9345,13 @@
         <v>2015</v>
       </c>
       <c r="B90" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C90" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D90" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E90">
         <v>1.204819277108434</v>
@@ -9185,13 +9422,13 @@
         <v>2016</v>
       </c>
       <c r="B91" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="C91" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="D91" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E91">
         <v>1.515151515151515</v>
@@ -9262,13 +9499,13 @@
         <v>2016</v>
       </c>
       <c r="B92" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C92" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D92" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -9339,13 +9576,13 @@
         <v>2016</v>
       </c>
       <c r="B93" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="C93" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="D93" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -9416,13 +9653,13 @@
         <v>2016</v>
       </c>
       <c r="B94" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="C94" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="D94" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -9493,13 +9730,13 @@
         <v>2016</v>
       </c>
       <c r="B95" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="C95" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D95" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E95">
         <v>2.02020202020202</v>
@@ -9570,13 +9807,13 @@
         <v>2016</v>
       </c>
       <c r="B96" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="C96" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="D96" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -9647,13 +9884,13 @@
         <v>2016</v>
       </c>
       <c r="B97" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="C97" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D97" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -9724,13 +9961,13 @@
         <v>2016</v>
       </c>
       <c r="B98" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="C98" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="D98" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -9801,13 +10038,13 @@
         <v>2016</v>
       </c>
       <c r="B99" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="C99" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="D99" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -9878,13 +10115,13 @@
         <v>2016</v>
       </c>
       <c r="B100" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="C100" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D100" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -9955,13 +10192,13 @@
         <v>2016</v>
       </c>
       <c r="B101" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C101" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D101" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -10032,13 +10269,13 @@
         <v>2016</v>
       </c>
       <c r="B102" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="C102" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="D102" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -10109,13 +10346,13 @@
         <v>2016</v>
       </c>
       <c r="B103" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="C103" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D103" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E103">
         <v>7.82122905027933</v>
@@ -10186,13 +10423,13 @@
         <v>2016</v>
       </c>
       <c r="B104" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="C104" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D104" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -10263,13 +10500,13 @@
         <v>2017</v>
       </c>
       <c r="B105" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="C105" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="D105" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E105">
         <v>1.470588235294118</v>
@@ -10340,13 +10577,13 @@
         <v>2017</v>
       </c>
       <c r="B106" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="C106" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="D106" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -10417,13 +10654,13 @@
         <v>2017</v>
       </c>
       <c r="B107" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C107" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="D107" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -10494,13 +10731,13 @@
         <v>2017</v>
       </c>
       <c r="B108" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="C108" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="D108" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -10571,13 +10808,13 @@
         <v>2017</v>
       </c>
       <c r="B109" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="C109" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="D109" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -10648,13 +10885,13 @@
         <v>2017</v>
       </c>
       <c r="B110" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="C110" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="D110" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E110">
         <v>1.851851851851852</v>
@@ -10725,13 +10962,13 @@
         <v>2017</v>
       </c>
       <c r="B111" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="C111" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="D111" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E111">
         <v>0.6920415224913495</v>
@@ -10802,13 +11039,13 @@
         <v>2017</v>
       </c>
       <c r="B112" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C112" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="D112" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -10879,13 +11116,13 @@
         <v>2017</v>
       </c>
       <c r="B113" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C113" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="D113" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -10956,13 +11193,13 @@
         <v>2017</v>
       </c>
       <c r="B114" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C114" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D114" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -11033,13 +11270,13 @@
         <v>2017</v>
       </c>
       <c r="B115" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="C115" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D115" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -11110,13 +11347,13 @@
         <v>2017</v>
       </c>
       <c r="B116" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C116" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D116" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -11187,13 +11424,13 @@
         <v>2017</v>
       </c>
       <c r="B117" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="C117" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D117" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -11264,13 +11501,13 @@
         <v>2017</v>
       </c>
       <c r="B118" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C118" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D118" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -11341,13 +11578,13 @@
         <v>2018</v>
       </c>
       <c r="B119" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C119" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -11418,13 +11655,13 @@
         <v>2018</v>
       </c>
       <c r="B120" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="C120" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="D120" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -11495,13 +11732,13 @@
         <v>2018</v>
       </c>
       <c r="B121" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C121" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D121" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -11572,13 +11809,13 @@
         <v>2018</v>
       </c>
       <c r="B122" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="C122" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="D122" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -11649,13 +11886,13 @@
         <v>2018</v>
       </c>
       <c r="B123" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C123" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="D123" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E123">
         <v>1.244813278008299</v>
@@ -11726,13 +11963,13 @@
         <v>2018</v>
       </c>
       <c r="B124" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="D124" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -11803,13 +12040,13 @@
         <v>2018</v>
       </c>
       <c r="B125" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="C125" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D125" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E125">
         <v>1.913875598086124</v>
@@ -11880,13 +12117,13 @@
         <v>2018</v>
       </c>
       <c r="B126" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="C126" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="D126" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -11957,13 +12194,13 @@
         <v>2018</v>
       </c>
       <c r="B127" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="C127" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="D127" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -12034,13 +12271,13 @@
         <v>2018</v>
       </c>
       <c r="B128" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="C128" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D128" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -12111,13 +12348,13 @@
         <v>2018</v>
       </c>
       <c r="B129" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C129" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D129" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -12188,13 +12425,13 @@
         <v>2018</v>
       </c>
       <c r="B130" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="C130" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="D130" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -12265,13 +12502,13 @@
         <v>2018</v>
       </c>
       <c r="B131" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="C131" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="D131" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E131">
         <v>0.6060606060606061</v>
@@ -12342,13 +12579,13 @@
         <v>2018</v>
       </c>
       <c r="B132" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="C132" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D132" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E132">
         <v>1.621621621621622</v>
@@ -12419,13 +12656,13 @@
         <v>2019</v>
       </c>
       <c r="B133" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="C133" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="D133" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -12496,13 +12733,13 @@
         <v>2019</v>
       </c>
       <c r="B134" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="C134" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="D134" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E134">
         <v>2.803738317757009</v>
@@ -12573,13 +12810,13 @@
         <v>2019</v>
       </c>
       <c r="B135" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="C135" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="D135" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E135">
         <v>1.393728222996516</v>
@@ -12650,13 +12887,13 @@
         <v>2019</v>
       </c>
       <c r="B136" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="C136" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="D136" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -12727,13 +12964,13 @@
         <v>2019</v>
       </c>
       <c r="B137" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="C137" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="D137" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E137">
         <v>0.2754820936639119</v>
@@ -12804,13 +13041,13 @@
         <v>2019</v>
       </c>
       <c r="B138" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="C138" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="D138" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -12881,13 +13118,13 @@
         <v>2019</v>
       </c>
       <c r="B139" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="C139" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="D139" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -12958,13 +13195,13 @@
         <v>2019</v>
       </c>
       <c r="B140" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="C140" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="D140" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E140">
         <v>0.2590673575129534</v>
@@ -13035,13 +13272,13 @@
         <v>2019</v>
       </c>
       <c r="B141" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="C141" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="D141" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E141">
         <v>0.5050505050505051</v>
@@ -13112,13 +13349,13 @@
         <v>2019</v>
       </c>
       <c r="B142" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C142" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="D142" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -13189,13 +13426,13 @@
         <v>2019</v>
       </c>
       <c r="B143" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C143" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="D143" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E143">
         <v>0.9345794392523363</v>
@@ -13266,13 +13503,13 @@
         <v>2019</v>
       </c>
       <c r="B144" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="C144" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="D144" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -13343,13 +13580,13 @@
         <v>2019</v>
       </c>
       <c r="B145" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="C145" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="D145" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E145">
         <v>5.46875</v>
@@ -13420,13 +13657,13 @@
         <v>2020</v>
       </c>
       <c r="B146" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C146" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="D146" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E146">
         <v>1.923076923076923</v>
@@ -13497,13 +13734,13 @@
         <v>2020</v>
       </c>
       <c r="B147" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="C147" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="D147" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E147">
         <v>0.2597402597402597</v>
@@ -13574,13 +13811,13 @@
         <v>2020</v>
       </c>
       <c r="B148" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="C148" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="D148" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -13651,13 +13888,13 @@
         <v>2020</v>
       </c>
       <c r="B149" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="C149" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="D149" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E149">
         <v>1.395348837209302</v>
@@ -13728,13 +13965,13 @@
         <v>2020</v>
       </c>
       <c r="B150" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="C150" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D150" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E150">
         <v>0.5649717514124294</v>
@@ -13805,13 +14042,13 @@
         <v>2020</v>
       </c>
       <c r="B151" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C151" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="D151" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E151">
         <v>2.5</v>
@@ -13882,13 +14119,13 @@
         <v>2020</v>
       </c>
       <c r="B152" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="C152" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="D152" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E152">
         <v>2.604166666666667</v>
@@ -13959,13 +14196,13 @@
         <v>2020</v>
       </c>
       <c r="B153" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="C153" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="D153" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E153">
         <v>0.2036659877800407</v>
@@ -14036,13 +14273,13 @@
         <v>2020</v>
       </c>
       <c r="B154" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="C154" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="D154" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -14113,13 +14350,13 @@
         <v>2020</v>
       </c>
       <c r="B155" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="C155" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="D155" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -14190,13 +14427,13 @@
         <v>2020</v>
       </c>
       <c r="B156" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="C156" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D156" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E156">
         <v>0.5181347150259068</v>
@@ -14267,13 +14504,13 @@
         <v>2020</v>
       </c>
       <c r="B157" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="C157" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="D157" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -14344,13 +14581,13 @@
         <v>2020</v>
       </c>
       <c r="B158" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="C158" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="D158" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E158">
         <v>3.317535545023697</v>
@@ -14421,13 +14658,13 @@
         <v>2020</v>
       </c>
       <c r="B159" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="C159" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="D159" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E159">
         <v>0.4484304932735426</v>
@@ -14498,13 +14735,13 @@
         <v>2020</v>
       </c>
       <c r="B160" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="C160" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="D160" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -14575,13 +14812,13 @@
         <v>2021</v>
       </c>
       <c r="B161" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="C161" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="D161" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E161">
         <v>2.923976608187134</v>
@@ -14652,13 +14889,13 @@
         <v>2021</v>
       </c>
       <c r="B162" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="C162" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="D162" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E162">
         <v>1.31578947368421</v>
@@ -14729,13 +14966,13 @@
         <v>2021</v>
       </c>
       <c r="B163" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="C163" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="D163" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -14806,13 +15043,13 @@
         <v>2021</v>
       </c>
       <c r="B164" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="C164" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="D164" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -14883,13 +15120,13 @@
         <v>2021</v>
       </c>
       <c r="B165" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="C165" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="D165" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E165">
         <v>3.225806451612903</v>
@@ -14960,13 +15197,13 @@
         <v>2021</v>
       </c>
       <c r="B166" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="C166" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="D166" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -15037,13 +15274,13 @@
         <v>2021</v>
       </c>
       <c r="B167" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="C167" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="D167" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -15114,13 +15351,13 @@
         <v>2021</v>
       </c>
       <c r="B168" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="C168" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D168" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -15191,13 +15428,13 @@
         <v>2021</v>
       </c>
       <c r="B169" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="C169" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D169" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E169">
         <v>0.5050505050505051</v>
@@ -15268,13 +15505,13 @@
         <v>2021</v>
       </c>
       <c r="B170" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="C170" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="D170" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -15345,13 +15582,13 @@
         <v>2021</v>
       </c>
       <c r="B171" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="C171" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="D171" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E171">
         <v>0.9202453987730062</v>
@@ -15422,13 +15659,13 @@
         <v>2021</v>
       </c>
       <c r="B172" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="C172" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="D172" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -15499,13 +15736,13 @@
         <v>2022</v>
       </c>
       <c r="B173" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="C173" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="D173" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -15576,13 +15813,13 @@
         <v>2022</v>
       </c>
       <c r="B174" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="C174" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="D174" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E174">
         <v>1.025641025641026</v>
@@ -15653,13 +15890,13 @@
         <v>2022</v>
       </c>
       <c r="B175" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="C175" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="D175" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E175">
         <v>1.932367149758454</v>
@@ -15730,13 +15967,13 @@
         <v>2022</v>
       </c>
       <c r="B176" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="C176" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D176" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -15807,13 +16044,13 @@
         <v>2022</v>
       </c>
       <c r="B177" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="C177" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="D177" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E177">
         <v>0.5128205128205128</v>
@@ -15884,13 +16121,13 @@
         <v>2022</v>
       </c>
       <c r="B178" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="C178" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="D178" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -15961,13 +16198,13 @@
         <v>2022</v>
       </c>
       <c r="B179" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="C179" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="D179" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E179">
         <v>0.6644518272425249</v>
@@ -16038,13 +16275,13 @@
         <v>2022</v>
       </c>
       <c r="B180" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="C180" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="D180" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E180">
         <v>1.84331797235023</v>
@@ -16115,13 +16352,13 @@
         <v>2022</v>
       </c>
       <c r="B181" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="C181" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="D181" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E181">
         <v>3.041825095057034</v>
@@ -16192,13 +16429,13 @@
         <v>2022</v>
       </c>
       <c r="B182" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="C182" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="D182" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -16269,13 +16506,13 @@
         <v>2022</v>
       </c>
       <c r="B183" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="C183" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="D183" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E183">
         <v>0.353356890459364</v>
@@ -16346,13 +16583,13 @@
         <v>2022</v>
       </c>
       <c r="B184" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="C184" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="D184" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -16423,13 +16660,13 @@
         <v>2022</v>
       </c>
       <c r="B185" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="C185" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="D185" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -16500,13 +16737,13 @@
         <v>2022</v>
       </c>
       <c r="B186" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="C186" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="D186" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -16577,13 +16814,13 @@
         <v>2022</v>
       </c>
       <c r="B187" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="C187" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="D187" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E187">
         <v>0.398406374501992</v>
@@ -16654,13 +16891,13 @@
         <v>2023</v>
       </c>
       <c r="B188" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="C188" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="D188" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -16731,13 +16968,13 @@
         <v>2023</v>
       </c>
       <c r="B189" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="C189" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="D189" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -16808,13 +17045,13 @@
         <v>2023</v>
       </c>
       <c r="B190" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="C190" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="D190" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E190">
         <v>0.6172839506172839</v>
@@ -16885,13 +17122,13 @@
         <v>2023</v>
       </c>
       <c r="B191" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="C191" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="D191" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E191">
         <v>0.5</v>
@@ -16962,13 +17199,13 @@
         <v>2023</v>
       </c>
       <c r="B192" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="C192" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="D192" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E192">
         <v>1.376146788990826</v>
@@ -17039,13 +17276,13 @@
         <v>2023</v>
       </c>
       <c r="B193" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="C193" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="D193" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E193">
         <v>1.463414634146342</v>
@@ -17116,13 +17353,13 @@
         <v>2023</v>
       </c>
       <c r="B194" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="C194" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="D194" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E194">
         <v>0.2816901408450704</v>
@@ -17193,13 +17430,13 @@
         <v>2023</v>
       </c>
       <c r="B195" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C195" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="D195" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -17270,13 +17507,13 @@
         <v>2023</v>
       </c>
       <c r="B196" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="C196" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="D196" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E196">
         <v>0.6451612903225806</v>
@@ -17347,13 +17584,13 @@
         <v>2023</v>
       </c>
       <c r="B197" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="C197" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="D197" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -17424,13 +17661,13 @@
         <v>2023</v>
       </c>
       <c r="B198" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="C198" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D198" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E198">
         <v>0.7462686567164178</v>
@@ -17501,13 +17738,13 @@
         <v>2023</v>
       </c>
       <c r="B199" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="C199" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D199" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -17578,13 +17815,13 @@
         <v>2023</v>
       </c>
       <c r="B200" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="C200" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="D200" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -17655,13 +17892,13 @@
         <v>2024</v>
       </c>
       <c r="B201" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="C201" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="D201" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -17732,13 +17969,13 @@
         <v>2024</v>
       </c>
       <c r="B202" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="C202" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="D202" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -17809,13 +18046,13 @@
         <v>2024</v>
       </c>
       <c r="B203" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="C203" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="D203" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -17886,13 +18123,13 @@
         <v>2024</v>
       </c>
       <c r="B204" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="C204" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="D204" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E204">
         <v>0.5586592178770949</v>
@@ -17963,13 +18200,13 @@
         <v>2024</v>
       </c>
       <c r="B205" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="C205" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="D205" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E205">
         <v>2.352941176470588</v>
@@ -18040,13 +18277,13 @@
         <v>2024</v>
       </c>
       <c r="B206" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C206" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="D206" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -18117,13 +18354,13 @@
         <v>2024</v>
       </c>
       <c r="B207" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="C207" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="D207" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -18194,13 +18431,13 @@
         <v>2024</v>
       </c>
       <c r="B208" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="C208" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="D208" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -18271,13 +18508,13 @@
         <v>2024</v>
       </c>
       <c r="B209" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="C209" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="D209" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -18348,13 +18585,13 @@
         <v>2024</v>
       </c>
       <c r="B210" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="C210" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="D210" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -18425,13 +18662,13 @@
         <v>2024</v>
       </c>
       <c r="B211" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="C211" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="D211" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E211">
         <v>1.973684210526316</v>
@@ -18502,13 +18739,13 @@
         <v>2024</v>
       </c>
       <c r="B212" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C212" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="D212" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -18579,13 +18816,13 @@
         <v>2024</v>
       </c>
       <c r="B213" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="C213" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="D213" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E213">
         <v>1.15606936416185</v>
@@ -18656,13 +18893,13 @@
         <v>2025</v>
       </c>
       <c r="B214" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="C214" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="D214" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E214">
         <v>1.680672268907563</v>
@@ -18733,13 +18970,13 @@
         <v>2025</v>
       </c>
       <c r="B215" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="C215" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="D215" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E215">
         <v>1.530612244897959</v>
@@ -18810,13 +19047,13 @@
         <v>2025</v>
       </c>
       <c r="B216" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="C216" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="D216" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E216">
         <v>0.5128205128205128</v>
@@ -18887,13 +19124,13 @@
         <v>2025</v>
       </c>
       <c r="B217" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="C217" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="D217" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -18964,13 +19201,13 @@
         <v>2025</v>
       </c>
       <c r="B218" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="C218" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="D218" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -19041,13 +19278,13 @@
         <v>2025</v>
       </c>
       <c r="B219" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="C219" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="D219" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -19118,13 +19355,13 @@
         <v>2025</v>
       </c>
       <c r="B220" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="C220" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="D220" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -19195,13 +19432,13 @@
         <v>2025</v>
       </c>
       <c r="B221" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="C221" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="D221" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -19272,13 +19509,13 @@
         <v>2025</v>
       </c>
       <c r="B222" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="C222" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="D222" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -19349,13 +19586,13 @@
         <v>2025</v>
       </c>
       <c r="B223" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="C223" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="D223" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -19426,13 +19663,13 @@
         <v>2025</v>
       </c>
       <c r="B224" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="C224" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D224" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -19503,13 +19740,13 @@
         <v>2025</v>
       </c>
       <c r="B225" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="C225" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="D225" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -19580,13 +19817,13 @@
         <v>2025</v>
       </c>
       <c r="B226" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="C226" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="D226" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E226">
         <v>0</v>
